--- a/research/traditional_assets/database/data/argentina/argentina_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_real_estate_operations_services.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1582649201344188</v>
+        <v>0.1577402429139484</v>
       </c>
       <c r="C2">
-        <v>1745.077714980492</v>
+        <v>1736.685863491823</v>
       </c>
       <c r="D2">
-        <v>1713.877714980492</v>
+        <v>1721.910863491823</v>
       </c>
       <c r="E2">
-        <v>-396.5</v>
+        <v>-380.075</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>16.425</v>
       </c>
       <c r="G2">
         <v>31.2</v>
@@ -1445,28 +1445,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.8261775</v>
       </c>
       <c r="N2">
-        <v>193.7632653061225</v>
+        <v>192.9370878061225</v>
       </c>
       <c r="O2">
-        <v>67.81714285714285</v>
+        <v>67.52798073214285</v>
       </c>
       <c r="P2">
-        <v>125.9461224489796</v>
+        <v>125.4091070739796</v>
       </c>
       <c r="Q2">
-        <v>130.3461224489796</v>
+        <v>129.8091070739796</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1582649201344188</v>
+        <v>0.1590033261757054</v>
       </c>
       <c r="T2">
-        <v>0.5525820103960151</v>
+        <v>0.5562100741006354</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>234.5298259830635</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1577402429139484</v>
+        <v>0.1572155656934779</v>
       </c>
       <c r="C3">
-        <v>1736.685863491823</v>
+        <v>1728.369671270445</v>
       </c>
       <c r="D3">
-        <v>1721.910863491823</v>
+        <v>1730.019671270444</v>
       </c>
       <c r="E3">
-        <v>-380.075</v>
+        <v>-363.65</v>
       </c>
       <c r="F3">
-        <v>16.425</v>
+        <v>32.85</v>
       </c>
       <c r="G3">
         <v>31.2</v>
@@ -1527,28 +1527,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M3">
-        <v>0.8261775</v>
+        <v>1.652355</v>
       </c>
       <c r="N3">
-        <v>192.9370878061225</v>
+        <v>192.1109103061225</v>
       </c>
       <c r="O3">
-        <v>67.52798073214285</v>
+        <v>67.23881860714286</v>
       </c>
       <c r="P3">
-        <v>125.4091070739796</v>
+        <v>124.8720916989796</v>
       </c>
       <c r="Q3">
-        <v>129.8091070739796</v>
+        <v>129.2720916989796</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1590033261757054</v>
+        <v>0.1597568017280387</v>
       </c>
       <c r="T3">
-        <v>0.5562100741006354</v>
+        <v>0.5599121799216765</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>234.5298259830635</v>
+        <v>117.2649129915318</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1572155656934779</v>
+        <v>0.1566908884730074</v>
       </c>
       <c r="C4">
-        <v>1728.369671270445</v>
+        <v>1720.130212255648</v>
       </c>
       <c r="D4">
-        <v>1730.019671270444</v>
+        <v>1738.205212255648</v>
       </c>
       <c r="E4">
-        <v>-363.65</v>
+        <v>-347.225</v>
       </c>
       <c r="F4">
-        <v>32.85</v>
+        <v>49.275</v>
       </c>
       <c r="G4">
         <v>31.2</v>
@@ -1609,28 +1609,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M4">
-        <v>1.652355</v>
+        <v>2.4785325</v>
       </c>
       <c r="N4">
-        <v>192.1109103061225</v>
+        <v>191.2847328061225</v>
       </c>
       <c r="O4">
-        <v>67.23881860714286</v>
+        <v>66.94965648214286</v>
       </c>
       <c r="P4">
-        <v>124.8720916989796</v>
+        <v>124.3350763239796</v>
       </c>
       <c r="Q4">
-        <v>129.2720916989796</v>
+        <v>128.7350763239796</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1597568017280387</v>
+        <v>0.1605258128587705</v>
       </c>
       <c r="T4">
-        <v>0.5599121799216765</v>
+        <v>0.563690617821502</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>117.2649129915318</v>
+        <v>78.17660866102119</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1566908884730074</v>
+        <v>0.1561662112525369</v>
       </c>
       <c r="C5">
-        <v>1720.130212255648</v>
+        <v>1711.968580808609</v>
       </c>
       <c r="D5">
-        <v>1738.205212255648</v>
+        <v>1746.468580808609</v>
       </c>
       <c r="E5">
-        <v>-347.225</v>
+        <v>-330.8</v>
       </c>
       <c r="F5">
-        <v>49.275</v>
+        <v>65.7</v>
       </c>
       <c r="G5">
         <v>31.2</v>
@@ -1691,28 +1691,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M5">
-        <v>2.4785325</v>
+        <v>3.30471</v>
       </c>
       <c r="N5">
-        <v>191.2847328061225</v>
+        <v>190.4585553061225</v>
       </c>
       <c r="O5">
-        <v>66.94965648214286</v>
+        <v>66.66049435714285</v>
       </c>
       <c r="P5">
-        <v>124.3350763239796</v>
+        <v>123.7980609489796</v>
       </c>
       <c r="Q5">
-        <v>128.7350763239796</v>
+        <v>128.1980609489796</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1605258128587705</v>
+        <v>0.161310845054726</v>
       </c>
       <c r="T5">
-        <v>0.563690617821502</v>
+        <v>0.5675477731775738</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>78.17660866102119</v>
+        <v>58.63245649576588</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1561662112525369</v>
+        <v>0.1556415340320665</v>
       </c>
       <c r="C6">
-        <v>1711.968580808609</v>
+        <v>1703.885892200128</v>
       </c>
       <c r="D6">
-        <v>1746.468580808609</v>
+        <v>1754.810892200127</v>
       </c>
       <c r="E6">
-        <v>-330.8</v>
+        <v>-314.375</v>
       </c>
       <c r="F6">
-        <v>65.7</v>
+        <v>82.125</v>
       </c>
       <c r="G6">
         <v>31.2</v>
@@ -1773,28 +1773,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M6">
-        <v>3.30471</v>
+        <v>4.1308875</v>
       </c>
       <c r="N6">
-        <v>190.4585553061225</v>
+        <v>189.6323778061225</v>
       </c>
       <c r="O6">
-        <v>66.66049435714285</v>
+        <v>66.37133223214286</v>
       </c>
       <c r="P6">
-        <v>123.7980609489796</v>
+        <v>123.2610455739796</v>
       </c>
       <c r="Q6">
-        <v>128.1980609489796</v>
+        <v>127.6610455739796</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.161310845054726</v>
+        <v>0.1621124042442805</v>
       </c>
       <c r="T6">
-        <v>0.5675477731775738</v>
+        <v>0.5714861318042997</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>58.63245649576588</v>
+        <v>46.9059651966127</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1556415340320665</v>
+        <v>0.155116856811596</v>
       </c>
       <c r="C7">
-        <v>1703.885892200128</v>
+        <v>1695.883283112424</v>
       </c>
       <c r="D7">
-        <v>1754.810892200127</v>
+        <v>1763.233283112424</v>
       </c>
       <c r="E7">
-        <v>-314.375</v>
+        <v>-297.95</v>
       </c>
       <c r="F7">
-        <v>82.125</v>
+        <v>98.55000000000001</v>
       </c>
       <c r="G7">
         <v>31.2</v>
@@ -1855,28 +1855,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M7">
-        <v>4.1308875</v>
+        <v>4.957065</v>
       </c>
       <c r="N7">
-        <v>189.6323778061225</v>
+        <v>188.8062003061225</v>
       </c>
       <c r="O7">
-        <v>66.37133223214286</v>
+        <v>66.08217010714286</v>
       </c>
       <c r="P7">
-        <v>123.2610455739796</v>
+        <v>122.7240301989796</v>
       </c>
       <c r="Q7">
-        <v>127.6610455739796</v>
+        <v>127.1240301989796</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1621124042442805</v>
+        <v>0.1629310178846766</v>
       </c>
       <c r="T7">
-        <v>0.5714861318042997</v>
+        <v>0.5755082852954242</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>46.9059651966127</v>
+        <v>39.08830433051059</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.155116856811596</v>
+        <v>0.1545921795911256</v>
       </c>
       <c r="C8">
-        <v>1695.883283112424</v>
+        <v>1687.961912155444</v>
       </c>
       <c r="D8">
-        <v>1763.233283112424</v>
+        <v>1771.736912155443</v>
       </c>
       <c r="E8">
-        <v>-297.95</v>
+        <v>-281.525</v>
       </c>
       <c r="F8">
-        <v>98.55</v>
+        <v>114.975</v>
       </c>
       <c r="G8">
         <v>31.2</v>
@@ -1937,28 +1937,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M8">
-        <v>4.957064999999999</v>
+        <v>5.783242499999999</v>
       </c>
       <c r="N8">
-        <v>188.8062003061225</v>
+        <v>187.9800228061225</v>
       </c>
       <c r="O8">
-        <v>66.08217010714286</v>
+        <v>65.79300798214285</v>
       </c>
       <c r="P8">
-        <v>122.7240301989796</v>
+        <v>122.1870148239796</v>
       </c>
       <c r="Q8">
-        <v>127.1240301989796</v>
+        <v>126.5870148239796</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1629310178846766</v>
+        <v>0.1637672361194898</v>
       </c>
       <c r="T8">
-        <v>0.5755082852954242</v>
+        <v>0.5796169367110888</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>39.0883043305106</v>
+        <v>33.50426085472336</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1545921795911256</v>
+        <v>0.1540675023706551</v>
       </c>
       <c r="C9">
-        <v>1687.961912155444</v>
+        <v>1680.122960398176</v>
       </c>
       <c r="D9">
-        <v>1771.736912155443</v>
+        <v>1780.322960398177</v>
       </c>
       <c r="E9">
-        <v>-281.525</v>
+        <v>-265.1</v>
       </c>
       <c r="F9">
-        <v>114.975</v>
+        <v>131.4</v>
       </c>
       <c r="G9">
         <v>31.2</v>
@@ -2019,28 +2019,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M9">
-        <v>5.7832425</v>
+        <v>6.60942</v>
       </c>
       <c r="N9">
-        <v>187.9800228061225</v>
+        <v>187.1538453061225</v>
       </c>
       <c r="O9">
-        <v>65.79300798214285</v>
+        <v>65.50384585714286</v>
       </c>
       <c r="P9">
-        <v>122.1870148239796</v>
+        <v>121.6499994489796</v>
       </c>
       <c r="Q9">
-        <v>126.5870148239796</v>
+        <v>126.0499994489796</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1637672361194898</v>
+        <v>0.1646216330115816</v>
       </c>
       <c r="T9">
-        <v>0.5796169367110888</v>
+        <v>0.5838149066357897</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.50426085472336</v>
+        <v>29.31622824788294</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1540675023706551</v>
+        <v>0.1535428251501846</v>
       </c>
       <c r="C10">
-        <v>1680.122960398176</v>
+        <v>1672.367631915509</v>
       </c>
       <c r="D10">
-        <v>1780.322960398177</v>
+        <v>1788.992631915509</v>
       </c>
       <c r="E10">
-        <v>-265.1</v>
+        <v>-248.675</v>
       </c>
       <c r="F10">
-        <v>131.4</v>
+        <v>147.825</v>
       </c>
       <c r="G10">
         <v>31.2</v>
@@ -2101,28 +2101,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M10">
-        <v>6.60942</v>
+        <v>7.435597499999999</v>
       </c>
       <c r="N10">
-        <v>187.1538453061225</v>
+        <v>186.3276678061225</v>
       </c>
       <c r="O10">
-        <v>65.50384585714286</v>
+        <v>65.21468373214286</v>
       </c>
       <c r="P10">
-        <v>121.6499994489796</v>
+        <v>121.1129840739796</v>
       </c>
       <c r="Q10">
-        <v>126.0499994489796</v>
+        <v>125.5129840739796</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1646216330115816</v>
+        <v>0.1654948078573457</v>
       </c>
       <c r="T10">
-        <v>0.5838149066357897</v>
+        <v>0.5881051396357588</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>29.31622824788294</v>
+        <v>26.05886955367373</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1535428251501846</v>
+        <v>0.1530181479297142</v>
       </c>
       <c r="C11">
-        <v>1672.367631915509</v>
+        <v>1664.697154351121</v>
       </c>
       <c r="D11">
-        <v>1788.992631915509</v>
+        <v>1797.747154351121</v>
       </c>
       <c r="E11">
-        <v>-248.675</v>
+        <v>-232.25</v>
       </c>
       <c r="F11">
-        <v>147.825</v>
+        <v>164.25</v>
       </c>
       <c r="G11">
         <v>31.2</v>
@@ -2183,28 +2183,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M11">
-        <v>7.435597499999999</v>
+        <v>8.261775</v>
       </c>
       <c r="N11">
-        <v>186.3276678061225</v>
+        <v>185.5014903061225</v>
       </c>
       <c r="O11">
-        <v>65.21468373214286</v>
+        <v>64.92552160714285</v>
       </c>
       <c r="P11">
-        <v>121.1129840739796</v>
+        <v>120.5759686989796</v>
       </c>
       <c r="Q11">
-        <v>125.5129840739796</v>
+        <v>124.9759686989796</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1654948078573457</v>
+        <v>0.1663873865885713</v>
       </c>
       <c r="T11">
-        <v>0.5881051396357588</v>
+        <v>0.5924907111468384</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.05886955367373</v>
+        <v>23.45298259830635</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1530181479297142</v>
+        <v>0.1524934707092437</v>
       </c>
       <c r="C12">
-        <v>1664.697154351121</v>
+        <v>1657.112779497004</v>
       </c>
       <c r="D12">
-        <v>1797.747154351121</v>
+        <v>1806.587779497004</v>
       </c>
       <c r="E12">
-        <v>-232.25</v>
+        <v>-215.825</v>
       </c>
       <c r="F12">
-        <v>164.25</v>
+        <v>180.675</v>
       </c>
       <c r="G12">
         <v>31.2</v>
@@ -2265,28 +2265,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M12">
-        <v>8.261775</v>
+        <v>9.0879525</v>
       </c>
       <c r="N12">
-        <v>185.5014903061225</v>
+        <v>184.6753128061225</v>
       </c>
       <c r="O12">
-        <v>64.92552160714285</v>
+        <v>64.63635948214286</v>
       </c>
       <c r="P12">
-        <v>120.5759686989796</v>
+        <v>120.0389533239796</v>
       </c>
       <c r="Q12">
-        <v>124.9759686989796</v>
+        <v>124.4389533239796</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1663873865885713</v>
+        <v>0.1673000232688132</v>
       </c>
       <c r="T12">
-        <v>0.5924907111468384</v>
+        <v>0.5969748348267062</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.45298259830635</v>
+        <v>21.32089327118759</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1524934707092437</v>
+        <v>0.1519687934887732</v>
       </c>
       <c r="C13">
-        <v>1657.112779497004</v>
+        <v>1649.615783890147</v>
       </c>
       <c r="D13">
-        <v>1806.587779497004</v>
+        <v>1815.515783890147</v>
       </c>
       <c r="E13">
-        <v>-215.825</v>
+        <v>-199.4</v>
       </c>
       <c r="F13">
-        <v>180.675</v>
+        <v>197.1</v>
       </c>
       <c r="G13">
         <v>31.2</v>
@@ -2347,28 +2347,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M13">
-        <v>9.0879525</v>
+        <v>9.914129999999998</v>
       </c>
       <c r="N13">
-        <v>184.6753128061225</v>
+        <v>183.8491353061225</v>
       </c>
       <c r="O13">
-        <v>64.63635948214286</v>
+        <v>64.34719735714286</v>
       </c>
       <c r="P13">
-        <v>120.0389533239796</v>
+        <v>119.5019379489796</v>
       </c>
       <c r="Q13">
-        <v>124.4389533239796</v>
+        <v>123.9019379489796</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1673000232688132</v>
+        <v>0.1682334016917878</v>
       </c>
       <c r="T13">
-        <v>0.5969748348267062</v>
+        <v>0.6015608704083891</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.32089327118759</v>
+        <v>19.5441521652553</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1519687934887732</v>
+        <v>0.1514441162683027</v>
       </c>
       <c r="C14">
-        <v>1649.615783890147</v>
+        <v>1642.207469427017</v>
       </c>
       <c r="D14">
-        <v>1815.515783890147</v>
+        <v>1824.532469427017</v>
       </c>
       <c r="E14">
-        <v>-199.4</v>
+        <v>-182.975</v>
       </c>
       <c r="F14">
-        <v>197.1</v>
+        <v>213.525</v>
       </c>
       <c r="G14">
         <v>31.2</v>
@@ -2429,28 +2429,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M14">
-        <v>9.914129999999998</v>
+        <v>10.7403075</v>
       </c>
       <c r="N14">
-        <v>183.8491353061225</v>
+        <v>183.0229578061225</v>
       </c>
       <c r="O14">
-        <v>64.34719735714286</v>
+        <v>64.05803523214286</v>
       </c>
       <c r="P14">
-        <v>119.5019379489796</v>
+        <v>118.9649225739796</v>
       </c>
       <c r="Q14">
-        <v>123.9019379489796</v>
+        <v>123.3649225739796</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1682334016917878</v>
+        <v>0.1691882370900032</v>
       </c>
       <c r="T14">
-        <v>0.6015608704083891</v>
+        <v>0.6062523320953981</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.5441521652553</v>
+        <v>18.04075584485104</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1514441162683027</v>
+        <v>0.1509194390478323</v>
       </c>
       <c r="C15">
-        <v>1642.207469427017</v>
+        <v>1634.889163996433</v>
       </c>
       <c r="D15">
-        <v>1824.532469427017</v>
+        <v>1833.639163996433</v>
       </c>
       <c r="E15">
-        <v>-182.975</v>
+        <v>-166.55</v>
       </c>
       <c r="F15">
-        <v>213.525</v>
+        <v>229.95</v>
       </c>
       <c r="G15">
         <v>31.2</v>
@@ -2511,28 +2511,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M15">
-        <v>10.7403075</v>
+        <v>11.566485</v>
       </c>
       <c r="N15">
-        <v>183.0229578061225</v>
+        <v>182.1967803061225</v>
       </c>
       <c r="O15">
-        <v>64.05803523214286</v>
+        <v>63.76887310714286</v>
       </c>
       <c r="P15">
-        <v>118.9649225739796</v>
+        <v>118.4279071989796</v>
       </c>
       <c r="Q15">
-        <v>123.3649225739796</v>
+        <v>122.8279071989796</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1691882370900032</v>
+        <v>0.1701652779625957</v>
       </c>
       <c r="T15">
-        <v>0.6062523320953981</v>
+        <v>0.6110528975425702</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.04075584485104</v>
+        <v>16.75213042736168</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1509194390478323</v>
+        <v>0.1503947618273618</v>
       </c>
       <c r="C16">
-        <v>1634.889163996433</v>
+        <v>1627.662222131499</v>
       </c>
       <c r="D16">
-        <v>1833.639163996433</v>
+        <v>1842.837222131499</v>
       </c>
       <c r="E16">
-        <v>-166.55</v>
+        <v>-150.125</v>
       </c>
       <c r="F16">
-        <v>229.95</v>
+        <v>246.375</v>
       </c>
       <c r="G16">
         <v>31.2</v>
@@ -2593,28 +2593,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M16">
-        <v>11.566485</v>
+        <v>12.3926625</v>
       </c>
       <c r="N16">
-        <v>182.1967803061225</v>
+        <v>181.3706028061225</v>
       </c>
       <c r="O16">
-        <v>63.76887310714286</v>
+        <v>63.47971098214285</v>
       </c>
       <c r="P16">
-        <v>118.4279071989796</v>
+        <v>117.8908918239796</v>
       </c>
       <c r="Q16">
-        <v>122.8279071989796</v>
+        <v>122.2908918239796</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1701652779625957</v>
+        <v>0.1711653080321904</v>
       </c>
       <c r="T16">
-        <v>0.6110528975425702</v>
+        <v>0.6159664174708521</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.75213042736168</v>
+        <v>15.63532173220423</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1503947618273618</v>
+        <v>0.1498700846068914</v>
       </c>
       <c r="C17">
-        <v>1627.662222131499</v>
+        <v>1620.528025681239</v>
       </c>
       <c r="D17">
-        <v>1842.837222131499</v>
+        <v>1852.128025681239</v>
       </c>
       <c r="E17">
-        <v>-150.125</v>
+        <v>-133.7</v>
       </c>
       <c r="F17">
-        <v>246.375</v>
+        <v>262.8</v>
       </c>
       <c r="G17">
         <v>31.2</v>
@@ -2675,28 +2675,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M17">
-        <v>12.3926625</v>
+        <v>13.21884</v>
       </c>
       <c r="N17">
-        <v>181.3706028061225</v>
+        <v>180.5444253061225</v>
       </c>
       <c r="O17">
-        <v>63.47971098214285</v>
+        <v>63.19054885714286</v>
       </c>
       <c r="P17">
-        <v>117.8908918239796</v>
+        <v>117.3538764489796</v>
       </c>
       <c r="Q17">
-        <v>122.2908918239796</v>
+        <v>121.7538764489796</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1711653080321904</v>
+        <v>0.1721891483415374</v>
       </c>
       <c r="T17">
-        <v>0.6159664174708521</v>
+        <v>0.620996925968855</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.63532173220423</v>
+        <v>14.65811412394147</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1498700846068914</v>
+        <v>0.1493454073864209</v>
       </c>
       <c r="C18">
-        <v>1620.528025681239</v>
+        <v>1613.487984502671</v>
       </c>
       <c r="D18">
-        <v>1852.128025681239</v>
+        <v>1861.512984502671</v>
       </c>
       <c r="E18">
-        <v>-133.7</v>
+        <v>-117.275</v>
       </c>
       <c r="F18">
-        <v>262.8</v>
+        <v>279.225</v>
       </c>
       <c r="G18">
         <v>31.2</v>
@@ -2757,28 +2757,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M18">
-        <v>13.21884</v>
+        <v>14.0450175</v>
       </c>
       <c r="N18">
-        <v>180.5444253061225</v>
+        <v>179.7182478061225</v>
       </c>
       <c r="O18">
-        <v>63.19054885714286</v>
+        <v>62.90138673214286</v>
       </c>
       <c r="P18">
-        <v>117.3538764489796</v>
+        <v>116.8168610739796</v>
       </c>
       <c r="Q18">
-        <v>121.7538764489796</v>
+        <v>121.2168610739796</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1721891483415374</v>
+        <v>0.1732376595017119</v>
       </c>
       <c r="T18">
-        <v>0.620996925968855</v>
+        <v>0.626148651539099</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.65811412394147</v>
+        <v>13.79587211665079</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1493454073864209</v>
+        <v>0.1488207301659504</v>
       </c>
       <c r="C19">
-        <v>1613.487984502671</v>
+        <v>1606.543537174014</v>
       </c>
       <c r="D19">
-        <v>1861.512984502671</v>
+        <v>1870.993537174014</v>
       </c>
       <c r="E19">
-        <v>-117.275</v>
+        <v>-100.85</v>
       </c>
       <c r="F19">
-        <v>279.225</v>
+        <v>295.65</v>
       </c>
       <c r="G19">
         <v>31.2</v>
@@ -2839,28 +2839,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M19">
-        <v>14.0450175</v>
+        <v>14.871195</v>
       </c>
       <c r="N19">
-        <v>179.7182478061225</v>
+        <v>178.8920703061225</v>
       </c>
       <c r="O19">
-        <v>62.90138673214286</v>
+        <v>62.61222460714286</v>
       </c>
       <c r="P19">
-        <v>116.8168610739796</v>
+        <v>116.2798456989796</v>
       </c>
       <c r="Q19">
-        <v>121.2168610739796</v>
+        <v>120.6798456989796</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1732376595017119</v>
+        <v>0.1743117441048176</v>
       </c>
       <c r="T19">
-        <v>0.626148651539099</v>
+        <v>0.6314260289525196</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.79587211665079</v>
+        <v>13.02943477683686</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1488207301659505</v>
+        <v>0.14848130294548</v>
       </c>
       <c r="C20">
-        <v>1606.543537174014</v>
+        <v>1596.303364573198</v>
       </c>
       <c r="D20">
-        <v>1870.993537174014</v>
+        <v>1877.178364573198</v>
       </c>
       <c r="E20">
-        <v>-100.85</v>
+        <v>-84.42500000000001</v>
       </c>
       <c r="F20">
-        <v>295.65</v>
+        <v>312.075</v>
       </c>
       <c r="G20">
         <v>31.2</v>
@@ -2921,45 +2921,45 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M20">
-        <v>14.871195</v>
+        <v>16.165485</v>
       </c>
       <c r="N20">
-        <v>178.8920703061225</v>
+        <v>177.5977803061225</v>
       </c>
       <c r="O20">
-        <v>62.61222460714286</v>
+        <v>62.15922310714286</v>
       </c>
       <c r="P20">
-        <v>116.2798456989796</v>
+        <v>115.4385571989796</v>
       </c>
       <c r="Q20">
-        <v>120.6798456989796</v>
+        <v>119.8385571989796</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1743117441048176</v>
+        <v>0.1754123493154074</v>
       </c>
       <c r="T20">
-        <v>0.6314260289525196</v>
+        <v>0.6368337119810865</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.35</v>
       </c>
       <c r="W20">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.02943477683686</v>
+        <v>11.98623272398709</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.14848130294548</v>
+        <v>0.1479663757250095</v>
       </c>
       <c r="C21">
-        <v>1596.303364573198</v>
+        <v>1589.339503139948</v>
       </c>
       <c r="D21">
-        <v>1877.178364573198</v>
+        <v>1886.639503139948</v>
       </c>
       <c r="E21">
-        <v>-84.42500000000001</v>
+        <v>-68</v>
       </c>
       <c r="F21">
-        <v>312.075</v>
+        <v>328.5</v>
       </c>
       <c r="G21">
         <v>31.2</v>
@@ -3003,28 +3003,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M21">
-        <v>16.165485</v>
+        <v>17.0163</v>
       </c>
       <c r="N21">
-        <v>177.5977803061225</v>
+        <v>176.7469653061225</v>
       </c>
       <c r="O21">
-        <v>62.15922310714286</v>
+        <v>61.86143785714286</v>
       </c>
       <c r="P21">
-        <v>115.4385571989796</v>
+        <v>114.8855274489796</v>
       </c>
       <c r="Q21">
-        <v>119.8385571989796</v>
+        <v>119.2855274489796</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1754123493154074</v>
+        <v>0.1765404696562619</v>
       </c>
       <c r="T21">
-        <v>0.6368337119810865</v>
+        <v>0.6423765870853676</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.98623272398709</v>
+        <v>11.38692108778774</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1479663757250095</v>
+        <v>0.1474514485045391</v>
       </c>
       <c r="C22">
-        <v>1589.339503139948</v>
+        <v>1582.471494699575</v>
       </c>
       <c r="D22">
-        <v>1886.639503139948</v>
+        <v>1896.196494699574</v>
       </c>
       <c r="E22">
-        <v>-68</v>
+        <v>-51.57499999999999</v>
       </c>
       <c r="F22">
-        <v>328.5</v>
+        <v>344.925</v>
       </c>
       <c r="G22">
         <v>31.2</v>
@@ -3085,28 +3085,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M22">
-        <v>17.0163</v>
+        <v>17.867115</v>
       </c>
       <c r="N22">
-        <v>176.7469653061225</v>
+        <v>175.8961503061225</v>
       </c>
       <c r="O22">
-        <v>61.86143785714286</v>
+        <v>61.56365260714286</v>
       </c>
       <c r="P22">
-        <v>114.8855274489796</v>
+        <v>114.3324976989796</v>
       </c>
       <c r="Q22">
-        <v>119.2855274489796</v>
+        <v>118.7324976989796</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1765404696562619</v>
+        <v>0.1776971500057456</v>
       </c>
       <c r="T22">
-        <v>0.6423765870853676</v>
+        <v>0.6480597881416557</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.38692108778774</v>
+        <v>10.84468675027403</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1474514485045391</v>
+        <v>0.1469365212840686</v>
       </c>
       <c r="C23">
-        <v>1582.471494699575</v>
+        <v>1575.700803331953</v>
       </c>
       <c r="D23">
-        <v>1896.196494699574</v>
+        <v>1905.850803331952</v>
       </c>
       <c r="E23">
-        <v>-51.57499999999999</v>
+        <v>-35.14999999999998</v>
       </c>
       <c r="F23">
-        <v>344.925</v>
+        <v>361.35</v>
       </c>
       <c r="G23">
         <v>31.2</v>
@@ -3167,28 +3167,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M23">
-        <v>17.867115</v>
+        <v>18.71793</v>
       </c>
       <c r="N23">
-        <v>175.8961503061225</v>
+        <v>175.0453353061225</v>
       </c>
       <c r="O23">
-        <v>61.56365260714286</v>
+        <v>61.26586735714286</v>
       </c>
       <c r="P23">
-        <v>114.3324976989796</v>
+        <v>113.7794679489796</v>
       </c>
       <c r="Q23">
-        <v>118.7324976989796</v>
+        <v>118.1794679489796</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1776971500057456</v>
+        <v>0.178883488825729</v>
       </c>
       <c r="T23">
-        <v>0.6480597881416557</v>
+        <v>0.6538887123019512</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.84468675027403</v>
+        <v>10.3517464434434</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1469365212840686</v>
+        <v>0.1464215940635981</v>
       </c>
       <c r="C24">
-        <v>1575.700803331953</v>
+        <v>1569.028923086454</v>
       </c>
       <c r="D24">
-        <v>1905.850803331952</v>
+        <v>1915.603923086454</v>
       </c>
       <c r="E24">
-        <v>-35.14999999999998</v>
+        <v>-18.72499999999997</v>
       </c>
       <c r="F24">
-        <v>361.35</v>
+        <v>377.775</v>
       </c>
       <c r="G24">
         <v>31.2</v>
@@ -3249,28 +3249,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M24">
-        <v>18.71793</v>
+        <v>19.568745</v>
       </c>
       <c r="N24">
-        <v>175.0453353061225</v>
+        <v>174.1945203061225</v>
       </c>
       <c r="O24">
-        <v>61.26586735714286</v>
+        <v>60.96808210714286</v>
       </c>
       <c r="P24">
-        <v>113.7794679489796</v>
+        <v>113.2264381989796</v>
       </c>
       <c r="Q24">
-        <v>118.1794679489796</v>
+        <v>117.6264381989796</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.178883488825729</v>
+        <v>0.1801006416410365</v>
       </c>
       <c r="T24">
-        <v>0.6538887123019512</v>
+        <v>0.6598690370897868</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.3517464434434</v>
+        <v>9.901670511119772</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1464215940635981</v>
+        <v>0.1461718668431276</v>
       </c>
       <c r="C25">
-        <v>1569.028923086454</v>
+        <v>1557.369984118102</v>
       </c>
       <c r="D25">
-        <v>1915.603923086454</v>
+        <v>1920.369984118102</v>
       </c>
       <c r="E25">
-        <v>-18.72499999999997</v>
+        <v>-2.299999999999955</v>
       </c>
       <c r="F25">
-        <v>377.775</v>
+        <v>394.2</v>
       </c>
       <c r="G25">
         <v>31.2</v>
@@ -3331,45 +3331,45 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M25">
-        <v>19.568745</v>
+        <v>21.0897</v>
       </c>
       <c r="N25">
-        <v>174.1945203061225</v>
+        <v>172.6735653061225</v>
       </c>
       <c r="O25">
-        <v>60.96808210714286</v>
+        <v>60.43574785714286</v>
       </c>
       <c r="P25">
-        <v>113.2264381989796</v>
+        <v>112.2378174489796</v>
       </c>
       <c r="Q25">
-        <v>117.6264381989796</v>
+        <v>116.6378174489796</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1801006416410365</v>
+        <v>0.181349824793589</v>
       </c>
       <c r="T25">
-        <v>0.6598690370897868</v>
+        <v>0.6660067388457234</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.35</v>
       </c>
       <c r="W25">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>9.901670511119772</v>
+        <v>9.187578073947115</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1461718668431276</v>
+        <v>0.1456679896226572</v>
       </c>
       <c r="C26">
-        <v>1557.369984118102</v>
+        <v>1550.634081631013</v>
       </c>
       <c r="D26">
-        <v>1920.369984118102</v>
+        <v>1930.059081631013</v>
       </c>
       <c r="E26">
-        <v>-2.300000000000011</v>
+        <v>14.125</v>
       </c>
       <c r="F26">
-        <v>394.2</v>
+        <v>410.625</v>
       </c>
       <c r="G26">
         <v>31.2</v>
@@ -3413,28 +3413,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M26">
-        <v>21.0897</v>
+        <v>21.9684375</v>
       </c>
       <c r="N26">
-        <v>172.6735653061225</v>
+        <v>171.7948278061225</v>
       </c>
       <c r="O26">
-        <v>60.43574785714286</v>
+        <v>60.12818973214286</v>
       </c>
       <c r="P26">
-        <v>112.2378174489796</v>
+        <v>111.6666380739796</v>
       </c>
       <c r="Q26">
-        <v>116.6378174489796</v>
+        <v>116.0666380739796</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.181349824793589</v>
+        <v>0.1826323194968763</v>
       </c>
       <c r="T26">
-        <v>0.6660067388457234</v>
+        <v>0.6723081126484851</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.187578073947115</v>
+        <v>8.82007495098923</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1456679896226572</v>
+        <v>0.1451641124021867</v>
       </c>
       <c r="C27">
-        <v>1550.634081631013</v>
+        <v>1543.996446323204</v>
       </c>
       <c r="D27">
-        <v>1930.059081631013</v>
+        <v>1939.846446323204</v>
       </c>
       <c r="E27">
-        <v>14.125</v>
+        <v>30.55000000000001</v>
       </c>
       <c r="F27">
-        <v>410.625</v>
+        <v>427.05</v>
       </c>
       <c r="G27">
         <v>31.2</v>
@@ -3495,28 +3495,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M27">
-        <v>21.9684375</v>
+        <v>22.847175</v>
       </c>
       <c r="N27">
-        <v>171.7948278061225</v>
+        <v>170.9160903061225</v>
       </c>
       <c r="O27">
-        <v>60.12818973214286</v>
+        <v>59.82063160714286</v>
       </c>
       <c r="P27">
-        <v>111.6666380739796</v>
+        <v>111.0954586989796</v>
       </c>
       <c r="Q27">
-        <v>116.0666380739796</v>
+        <v>115.4954586989796</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1826323194968763</v>
+        <v>0.1839494762191712</v>
       </c>
       <c r="T27">
-        <v>0.6723081126484851</v>
+        <v>0.6787797938513213</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.82007495098923</v>
+        <v>8.480841299028107</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1451641124021867</v>
+        <v>0.1446602351817163</v>
       </c>
       <c r="C28">
-        <v>1543.996446323204</v>
+        <v>1537.458580758158</v>
       </c>
       <c r="D28">
-        <v>1939.846446323204</v>
+        <v>1949.733580758158</v>
       </c>
       <c r="E28">
-        <v>30.55000000000001</v>
+        <v>46.97500000000002</v>
       </c>
       <c r="F28">
-        <v>427.05</v>
+        <v>443.475</v>
       </c>
       <c r="G28">
         <v>31.2</v>
@@ -3577,28 +3577,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M28">
-        <v>22.847175</v>
+        <v>23.7259125</v>
       </c>
       <c r="N28">
-        <v>170.9160903061225</v>
+        <v>170.0373528061225</v>
       </c>
       <c r="O28">
-        <v>59.82063160714286</v>
+        <v>59.51307348214286</v>
       </c>
       <c r="P28">
-        <v>111.0954586989796</v>
+        <v>110.5242793239796</v>
       </c>
       <c r="Q28">
-        <v>115.4954586989796</v>
+        <v>114.9242793239796</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1839494762191712</v>
+        <v>0.1853027194270086</v>
       </c>
       <c r="T28">
-        <v>0.6787797938513213</v>
+        <v>0.6854287813884817</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.480841299028107</v>
+        <v>8.166736065730769</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1446602351817163</v>
+        <v>0.1441563579612458</v>
       </c>
       <c r="C29">
-        <v>1537.458580758158</v>
+        <v>1531.022018289746</v>
       </c>
       <c r="D29">
-        <v>1949.733580758158</v>
+        <v>1959.722018289746</v>
       </c>
       <c r="E29">
-        <v>46.97500000000002</v>
+        <v>63.40000000000003</v>
       </c>
       <c r="F29">
-        <v>443.475</v>
+        <v>459.9</v>
       </c>
       <c r="G29">
         <v>31.2</v>
@@ -3659,28 +3659,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M29">
-        <v>23.7259125</v>
+        <v>24.60465</v>
       </c>
       <c r="N29">
-        <v>170.0373528061225</v>
+        <v>169.1586153061225</v>
       </c>
       <c r="O29">
-        <v>59.51307348214286</v>
+        <v>59.20551535714286</v>
       </c>
       <c r="P29">
-        <v>110.5242793239796</v>
+        <v>109.9530999489796</v>
       </c>
       <c r="Q29">
-        <v>114.9242793239796</v>
+        <v>114.3530999489796</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1853027194270086</v>
+        <v>0.1866935527239525</v>
       </c>
       <c r="T29">
-        <v>0.6854287813884817</v>
+        <v>0.6922624630238966</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.166736065730769</v>
+        <v>7.875066920526097</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1441563579612458</v>
+        <v>0.1438032807407753</v>
       </c>
       <c r="C30">
-        <v>1531.022018289746</v>
+        <v>1521.657324821143</v>
       </c>
       <c r="D30">
-        <v>1959.722018289746</v>
+        <v>1966.782324821143</v>
       </c>
       <c r="E30">
-        <v>63.40000000000003</v>
+        <v>79.82500000000005</v>
       </c>
       <c r="F30">
-        <v>459.9</v>
+        <v>476.325</v>
       </c>
       <c r="G30">
         <v>31.2</v>
@@ -3741,45 +3741,45 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M30">
-        <v>24.60465</v>
+        <v>25.8644475</v>
       </c>
       <c r="N30">
-        <v>169.1586153061225</v>
+        <v>167.8988178061225</v>
       </c>
       <c r="O30">
-        <v>59.20551535714286</v>
+        <v>58.76458623214285</v>
       </c>
       <c r="P30">
-        <v>109.9530999489796</v>
+        <v>109.1342315739796</v>
       </c>
       <c r="Q30">
-        <v>114.3530999489796</v>
+        <v>113.5342315739796</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1866935527239525</v>
+        <v>0.1881235644236272</v>
       </c>
       <c r="T30">
-        <v>0.6922624630238966</v>
+        <v>0.6992886427335486</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.35</v>
       </c>
       <c r="W30">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.875066920526097</v>
+        <v>7.491490599446303</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1438032807407753</v>
+        <v>0.1433046035203048</v>
       </c>
       <c r="C31">
-        <v>1521.657324821143</v>
+        <v>1515.291229812312</v>
       </c>
       <c r="D31">
-        <v>1966.782324821143</v>
+        <v>1976.841229812312</v>
       </c>
       <c r="E31">
-        <v>79.82499999999999</v>
+        <v>96.25</v>
       </c>
       <c r="F31">
-        <v>476.325</v>
+        <v>492.75</v>
       </c>
       <c r="G31">
         <v>31.2</v>
@@ -3823,28 +3823,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M31">
-        <v>25.8644475</v>
+        <v>26.756325</v>
       </c>
       <c r="N31">
-        <v>167.8988178061225</v>
+        <v>167.0069403061225</v>
       </c>
       <c r="O31">
-        <v>58.76458623214285</v>
+        <v>58.45242910714286</v>
       </c>
       <c r="P31">
-        <v>109.1342315739796</v>
+        <v>108.5545111989796</v>
       </c>
       <c r="Q31">
-        <v>113.5342315739796</v>
+        <v>112.9545111989796</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1881235644236272</v>
+        <v>0.1895944336004355</v>
       </c>
       <c r="T31">
-        <v>0.6992886427335486</v>
+        <v>0.7065155704349049</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.491490599446304</v>
+        <v>7.241774246131427</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1433046035203048</v>
+        <v>0.1428059262998344</v>
       </c>
       <c r="C32">
-        <v>1515.291229812312</v>
+        <v>1509.028554191827</v>
       </c>
       <c r="D32">
-        <v>1976.841229812312</v>
+        <v>1987.003554191827</v>
       </c>
       <c r="E32">
-        <v>96.25</v>
+        <v>112.675</v>
       </c>
       <c r="F32">
-        <v>492.75</v>
+        <v>509.175</v>
       </c>
       <c r="G32">
         <v>31.2</v>
@@ -3905,28 +3905,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M32">
-        <v>26.756325</v>
+        <v>27.6482025</v>
       </c>
       <c r="N32">
-        <v>167.0069403061225</v>
+        <v>166.1150628061225</v>
       </c>
       <c r="O32">
-        <v>58.45242910714286</v>
+        <v>58.14027198214286</v>
       </c>
       <c r="P32">
-        <v>108.5545111989796</v>
+        <v>107.9747908239796</v>
       </c>
       <c r="Q32">
-        <v>112.9545111989796</v>
+        <v>112.3747908239796</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1895944336004355</v>
+        <v>0.1911079366664266</v>
       </c>
       <c r="T32">
-        <v>0.7065155704349049</v>
+        <v>0.713951974301518</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.241774246131427</v>
+        <v>7.008168625288478</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1428059262998344</v>
+        <v>0.1423072490793639</v>
       </c>
       <c r="C33">
-        <v>1509.028554191827</v>
+        <v>1502.870901141633</v>
       </c>
       <c r="D33">
-        <v>1987.003554191827</v>
+        <v>1997.270901141633</v>
       </c>
       <c r="E33">
-        <v>112.675</v>
+        <v>129.1</v>
       </c>
       <c r="F33">
-        <v>509.175</v>
+        <v>525.6</v>
       </c>
       <c r="G33">
         <v>31.2</v>
@@ -3987,28 +3987,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M33">
-        <v>27.6482025</v>
+        <v>28.54008</v>
       </c>
       <c r="N33">
-        <v>166.1150628061225</v>
+        <v>165.2231853061224</v>
       </c>
       <c r="O33">
-        <v>58.14027198214286</v>
+        <v>57.82811485714285</v>
       </c>
       <c r="P33">
-        <v>107.9747908239796</v>
+        <v>107.3950704489796</v>
       </c>
       <c r="Q33">
-        <v>112.3747908239796</v>
+        <v>111.7950704489796</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1911079366664266</v>
+        <v>0.1926659545284764</v>
       </c>
       <c r="T33">
-        <v>0.713951974301518</v>
+        <v>0.7216070959289138</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.008168625288478</v>
+        <v>6.789163355748212</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1423072490793639</v>
+        <v>0.1418085718588935</v>
       </c>
       <c r="C34">
-        <v>1502.870901141633</v>
+        <v>1496.819907151969</v>
       </c>
       <c r="D34">
-        <v>1997.270901141633</v>
+        <v>2007.644907151969</v>
       </c>
       <c r="E34">
-        <v>129.1</v>
+        <v>145.525</v>
       </c>
       <c r="F34">
-        <v>525.6</v>
+        <v>542.025</v>
       </c>
       <c r="G34">
         <v>31.2</v>
@@ -4069,28 +4069,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M34">
-        <v>28.54008</v>
+        <v>29.4319575</v>
       </c>
       <c r="N34">
-        <v>165.2231853061224</v>
+        <v>164.3313078061225</v>
       </c>
       <c r="O34">
-        <v>57.82811485714285</v>
+        <v>57.51595773214285</v>
       </c>
       <c r="P34">
-        <v>107.3950704489796</v>
+        <v>106.8153500739796</v>
       </c>
       <c r="Q34">
-        <v>111.7950704489796</v>
+        <v>111.2153500739796</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1926659545284764</v>
+        <v>0.1942704803864082</v>
       </c>
       <c r="T34">
-        <v>0.7216070959289138</v>
+        <v>0.7294907286496647</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.789163355748212</v>
+        <v>6.583431132846752</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1418085718588935</v>
+        <v>0.141309894638423</v>
       </c>
       <c r="C35">
-        <v>1496.819907151969</v>
+        <v>1490.877242890904</v>
       </c>
       <c r="D35">
-        <v>2007.644907151969</v>
+        <v>2018.127242890904</v>
       </c>
       <c r="E35">
-        <v>145.525</v>
+        <v>161.95</v>
       </c>
       <c r="F35">
-        <v>542.025</v>
+        <v>558.45</v>
       </c>
       <c r="G35">
         <v>31.2</v>
@@ -4151,28 +4151,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M35">
-        <v>29.4319575</v>
+        <v>30.323835</v>
       </c>
       <c r="N35">
-        <v>164.3313078061225</v>
+        <v>163.4394303061225</v>
       </c>
       <c r="O35">
-        <v>57.51595773214285</v>
+        <v>57.20380060714286</v>
       </c>
       <c r="P35">
-        <v>106.8153500739796</v>
+        <v>106.2356296989796</v>
       </c>
       <c r="Q35">
-        <v>111.2153500739796</v>
+        <v>110.6356296989796</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1942704803864082</v>
+        <v>0.1959236282400348</v>
       </c>
       <c r="T35">
-        <v>0.7294907286496647</v>
+        <v>0.7376132593316505</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.583431132846752</v>
+        <v>6.389800805410083</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.141309894638423</v>
+        <v>0.1408112174179525</v>
       </c>
       <c r="C36">
-        <v>1490.877242890904</v>
+        <v>1485.044614101278</v>
       </c>
       <c r="D36">
-        <v>2018.127242890904</v>
+        <v>2028.719614101278</v>
       </c>
       <c r="E36">
-        <v>161.95</v>
+        <v>178.375</v>
       </c>
       <c r="F36">
-        <v>558.45</v>
+        <v>574.875</v>
       </c>
       <c r="G36">
         <v>31.2</v>
@@ -4233,28 +4233,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M36">
-        <v>30.323835</v>
+        <v>31.2157125</v>
       </c>
       <c r="N36">
-        <v>163.4394303061225</v>
+        <v>162.5475528061225</v>
       </c>
       <c r="O36">
-        <v>57.20380060714286</v>
+        <v>56.89164348214286</v>
       </c>
       <c r="P36">
-        <v>106.2356296989796</v>
+        <v>105.6559093239796</v>
       </c>
       <c r="Q36">
-        <v>110.6356296989796</v>
+        <v>110.0559093239796</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1959236282400348</v>
+        <v>0.1976276421814654</v>
       </c>
       <c r="T36">
-        <v>0.7376132593316505</v>
+        <v>0.7459857140346204</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.389800805410083</v>
+        <v>6.207235068112652</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1408112174179525</v>
+        <v>0.1405465401974821</v>
       </c>
       <c r="C37">
-        <v>1485.044614101278</v>
+        <v>1474.286901449766</v>
       </c>
       <c r="D37">
-        <v>2028.719614101278</v>
+        <v>2034.386901449766</v>
       </c>
       <c r="E37">
-        <v>178.375</v>
+        <v>194.8000000000001</v>
       </c>
       <c r="F37">
-        <v>574.875</v>
+        <v>591.3000000000001</v>
       </c>
       <c r="G37">
         <v>31.2</v>
@@ -4315,45 +4315,45 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M37">
-        <v>31.2157125</v>
+        <v>32.69889000000001</v>
       </c>
       <c r="N37">
-        <v>162.5475528061225</v>
+        <v>161.0643753061225</v>
       </c>
       <c r="O37">
-        <v>56.89164348214286</v>
+        <v>56.37253135714285</v>
       </c>
       <c r="P37">
-        <v>105.6559093239796</v>
+        <v>104.6918439489796</v>
       </c>
       <c r="Q37">
-        <v>110.0559093239796</v>
+        <v>109.0918439489796</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1976276421814654</v>
+        <v>0.1993849065585657</v>
       </c>
       <c r="T37">
-        <v>0.7459857140346204</v>
+        <v>0.7546198079470581</v>
       </c>
       <c r="U37">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.35</v>
       </c>
       <c r="W37">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>6.207235068112652</v>
+        <v>5.925683266499946</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1405465401974821</v>
+        <v>0.1400543629770116</v>
       </c>
       <c r="C38">
-        <v>1474.286901449766</v>
+        <v>1468.485058393294</v>
       </c>
       <c r="D38">
-        <v>2034.386901449766</v>
+        <v>2045.010058393294</v>
       </c>
       <c r="E38">
-        <v>194.8</v>
+        <v>211.225</v>
       </c>
       <c r="F38">
-        <v>591.3</v>
+        <v>607.725</v>
       </c>
       <c r="G38">
         <v>31.2</v>
@@ -4397,28 +4397,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M38">
-        <v>32.69889</v>
+        <v>33.6071925</v>
       </c>
       <c r="N38">
-        <v>161.0643753061225</v>
+        <v>160.1560728061225</v>
       </c>
       <c r="O38">
-        <v>56.37253135714285</v>
+        <v>56.05462548214286</v>
       </c>
       <c r="P38">
-        <v>104.6918439489796</v>
+        <v>104.1014473239796</v>
       </c>
       <c r="Q38">
-        <v>109.0918439489796</v>
+        <v>108.5014473239796</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1993849065585657</v>
+        <v>0.2011979571063676</v>
       </c>
       <c r="T38">
-        <v>0.7546198079470581</v>
+        <v>0.7635280000789383</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.925683266499948</v>
+        <v>5.765529664702651</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1400543629770116</v>
+        <v>0.1395621857565411</v>
       </c>
       <c r="C39">
-        <v>1468.485058393294</v>
+        <v>1462.794741658759</v>
       </c>
       <c r="D39">
-        <v>2045.010058393294</v>
+        <v>2055.744741658759</v>
       </c>
       <c r="E39">
-        <v>211.225</v>
+        <v>227.65</v>
       </c>
       <c r="F39">
-        <v>607.725</v>
+        <v>624.15</v>
       </c>
       <c r="G39">
         <v>31.2</v>
@@ -4479,28 +4479,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M39">
-        <v>33.6071925</v>
+        <v>34.515495</v>
       </c>
       <c r="N39">
-        <v>160.1560728061225</v>
+        <v>159.2477703061224</v>
       </c>
       <c r="O39">
-        <v>56.05462548214286</v>
+        <v>55.73671960714285</v>
       </c>
       <c r="P39">
-        <v>104.1014473239796</v>
+        <v>103.5110506989796</v>
       </c>
       <c r="Q39">
-        <v>108.5014473239796</v>
+        <v>107.9110506989796</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2011979571063676</v>
+        <v>0.2030694931557115</v>
       </c>
       <c r="T39">
-        <v>0.7635280000789383</v>
+        <v>0.7727235532473308</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.765529664702651</v>
+        <v>5.613805199842055</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1395621857565411</v>
+        <v>0.1390700085360707</v>
       </c>
       <c r="C40">
-        <v>1462.794741658759</v>
+        <v>1457.217716788461</v>
       </c>
       <c r="D40">
-        <v>2055.744741658759</v>
+        <v>2066.592716788462</v>
       </c>
       <c r="E40">
-        <v>227.65</v>
+        <v>244.075</v>
       </c>
       <c r="F40">
-        <v>624.15</v>
+        <v>640.575</v>
       </c>
       <c r="G40">
         <v>31.2</v>
@@ -4561,28 +4561,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M40">
-        <v>34.515495</v>
+        <v>35.42379750000001</v>
       </c>
       <c r="N40">
-        <v>159.2477703061224</v>
+        <v>158.3394678061225</v>
       </c>
       <c r="O40">
-        <v>55.73671960714285</v>
+        <v>55.41881373214286</v>
       </c>
       <c r="P40">
-        <v>103.5110506989796</v>
+        <v>102.9206540739796</v>
       </c>
       <c r="Q40">
-        <v>107.9110506989796</v>
+        <v>107.3206540739796</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2030694931557115</v>
+        <v>0.2050023910427388</v>
       </c>
       <c r="T40">
-        <v>0.7727235532473308</v>
+        <v>0.7822205999622279</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.613805199842055</v>
+        <v>5.469861476769181</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1390700085360707</v>
+        <v>0.1385778313156002</v>
       </c>
       <c r="C41">
-        <v>1457.217716788461</v>
+        <v>1451.75578678881</v>
       </c>
       <c r="D41">
-        <v>2066.592716788462</v>
+        <v>2077.55578678881</v>
       </c>
       <c r="E41">
-        <v>244.075</v>
+        <v>260.5</v>
       </c>
       <c r="F41">
-        <v>640.575</v>
+        <v>657</v>
       </c>
       <c r="G41">
         <v>31.2</v>
@@ -4643,28 +4643,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M41">
-        <v>35.42379750000001</v>
+        <v>36.3321</v>
       </c>
       <c r="N41">
-        <v>158.3394678061225</v>
+        <v>157.4311653061225</v>
       </c>
       <c r="O41">
-        <v>55.41881373214286</v>
+        <v>55.10090785714286</v>
       </c>
       <c r="P41">
-        <v>102.9206540739796</v>
+        <v>102.3302574489796</v>
       </c>
       <c r="Q41">
-        <v>107.3206540739796</v>
+        <v>106.7302574489796</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2050023910427388</v>
+        <v>0.2069997188593337</v>
       </c>
       <c r="T41">
-        <v>0.7822205999622279</v>
+        <v>0.7920342149009549</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.469861476769181</v>
+        <v>5.333114939849952</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1385778313156002</v>
+        <v>0.1380856540951297</v>
       </c>
       <c r="C42">
-        <v>1451.75578678881</v>
+        <v>1446.410793129341</v>
       </c>
       <c r="D42">
-        <v>2077.55578678881</v>
+        <v>2088.635793129341</v>
       </c>
       <c r="E42">
-        <v>260.5</v>
+        <v>276.9250000000001</v>
       </c>
       <c r="F42">
-        <v>657</v>
+        <v>673.4250000000001</v>
       </c>
       <c r="G42">
         <v>31.2</v>
@@ -4725,28 +4725,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M42">
-        <v>36.3321</v>
+        <v>37.2404025</v>
       </c>
       <c r="N42">
-        <v>157.4311653061225</v>
+        <v>156.5228628061225</v>
       </c>
       <c r="O42">
-        <v>55.10090785714286</v>
+        <v>54.78300198214286</v>
       </c>
       <c r="P42">
-        <v>102.3302574489796</v>
+        <v>101.7398608239796</v>
       </c>
       <c r="Q42">
-        <v>106.7302574489796</v>
+        <v>106.1398608239796</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2069997188593337</v>
+        <v>0.2090647527036097</v>
       </c>
       <c r="T42">
-        <v>0.7920342149009549</v>
+        <v>0.8021804947528591</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.333114939849952</v>
+        <v>5.203038965707271</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1380856540951297</v>
+        <v>0.1375934768746593</v>
       </c>
       <c r="C43">
-        <v>1446.410793129341</v>
+        <v>1441.18461677387</v>
       </c>
       <c r="D43">
-        <v>2088.635793129341</v>
+        <v>2099.83461677387</v>
       </c>
       <c r="E43">
-        <v>276.9250000000001</v>
+        <v>293.35</v>
       </c>
       <c r="F43">
-        <v>673.4250000000001</v>
+        <v>689.85</v>
       </c>
       <c r="G43">
         <v>31.2</v>
@@ -4807,28 +4807,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M43">
-        <v>37.2404025</v>
+        <v>38.148705</v>
       </c>
       <c r="N43">
-        <v>156.5228628061225</v>
+        <v>155.6145603061225</v>
       </c>
       <c r="O43">
-        <v>54.78300198214286</v>
+        <v>54.46509610714286</v>
       </c>
       <c r="P43">
-        <v>101.7398608239796</v>
+        <v>101.1494641989796</v>
       </c>
       <c r="Q43">
-        <v>106.1398608239796</v>
+        <v>105.5494641989796</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2090647527036097</v>
+        <v>0.2112009946114815</v>
       </c>
       <c r="T43">
-        <v>0.8021804947528591</v>
+        <v>0.8126766463237945</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.203038965707271</v>
+        <v>5.079157085571383</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1375934768746593</v>
+        <v>0.1371012996541888</v>
       </c>
       <c r="C44">
-        <v>1441.18461677387</v>
+        <v>1436.079179245005</v>
       </c>
       <c r="D44">
-        <v>2099.83461677387</v>
+        <v>2111.154179245005</v>
       </c>
       <c r="E44">
-        <v>293.35</v>
+        <v>309.775</v>
       </c>
       <c r="F44">
-        <v>689.85</v>
+        <v>706.275</v>
       </c>
       <c r="G44">
         <v>31.2</v>
@@ -4889,28 +4889,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M44">
-        <v>38.148705</v>
+        <v>39.0570075</v>
       </c>
       <c r="N44">
-        <v>155.6145603061225</v>
+        <v>154.7062578061225</v>
       </c>
       <c r="O44">
-        <v>54.46509610714286</v>
+        <v>54.14719023214286</v>
       </c>
       <c r="P44">
-        <v>101.1494641989796</v>
+        <v>100.5590675739796</v>
       </c>
       <c r="Q44">
-        <v>105.5494641989796</v>
+        <v>104.9590675739796</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2112009946114815</v>
+        <v>0.2134121923757698</v>
       </c>
       <c r="T44">
-        <v>0.8126766463237945</v>
+        <v>0.8235410839147629</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.079157085571383</v>
+        <v>4.961037153348793</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1371012996541888</v>
+        <v>0.1366091224337183</v>
       </c>
       <c r="C45">
-        <v>1436.079179245005</v>
+        <v>1431.096443723266</v>
       </c>
       <c r="D45">
-        <v>2111.154179245005</v>
+        <v>2122.596443723266</v>
       </c>
       <c r="E45">
-        <v>309.775</v>
+        <v>326.2</v>
       </c>
       <c r="F45">
-        <v>706.275</v>
+        <v>722.7</v>
       </c>
       <c r="G45">
         <v>31.2</v>
@@ -4971,28 +4971,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M45">
-        <v>39.0570075</v>
+        <v>39.96531</v>
       </c>
       <c r="N45">
-        <v>154.7062578061225</v>
+        <v>153.7979553061224</v>
       </c>
       <c r="O45">
-        <v>54.14719023214286</v>
+        <v>53.82928435714285</v>
       </c>
       <c r="P45">
-        <v>100.5590675739796</v>
+        <v>99.96867094897959</v>
       </c>
       <c r="Q45">
-        <v>104.9590675739796</v>
+        <v>104.3686709489796</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2134121923757698</v>
+        <v>0.2157023614887827</v>
       </c>
       <c r="T45">
-        <v>0.8235410839147629</v>
+        <v>0.8347935371339799</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.961037153348793</v>
+        <v>4.848286308954502</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1366091224337183</v>
+        <v>0.1361169452132479</v>
       </c>
       <c r="C46">
-        <v>1431.096443723266</v>
+        <v>1426.238416182151</v>
       </c>
       <c r="D46">
-        <v>2122.596443723266</v>
+        <v>2134.163416182152</v>
       </c>
       <c r="E46">
-        <v>326.2</v>
+        <v>342.625</v>
       </c>
       <c r="F46">
-        <v>722.7</v>
+        <v>739.125</v>
       </c>
       <c r="G46">
         <v>31.2</v>
@@ -5053,28 +5053,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M46">
-        <v>39.96531</v>
+        <v>40.8736125</v>
       </c>
       <c r="N46">
-        <v>153.7979553061224</v>
+        <v>152.8896528061225</v>
       </c>
       <c r="O46">
-        <v>53.82928435714285</v>
+        <v>53.51137848214286</v>
       </c>
       <c r="P46">
-        <v>99.96867094897959</v>
+        <v>99.3782743239796</v>
       </c>
       <c r="Q46">
-        <v>104.3686709489796</v>
+        <v>103.7782743239796</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2157023614887827</v>
+        <v>0.2180758094786325</v>
       </c>
       <c r="T46">
-        <v>0.8347935371339799</v>
+        <v>0.8464551704702594</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.848286308954502</v>
+        <v>4.740546613199958</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1361169452132479</v>
+        <v>0.1356247679927774</v>
       </c>
       <c r="C47">
-        <v>1426.238416182151</v>
+        <v>1421.507146560511</v>
       </c>
       <c r="D47">
-        <v>2134.163416182152</v>
+        <v>2145.857146560511</v>
       </c>
       <c r="E47">
-        <v>342.625</v>
+        <v>359.0500000000001</v>
       </c>
       <c r="F47">
-        <v>739.125</v>
+        <v>755.5500000000001</v>
       </c>
       <c r="G47">
         <v>31.2</v>
@@ -5135,28 +5135,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M47">
-        <v>40.8736125</v>
+        <v>41.78191500000001</v>
       </c>
       <c r="N47">
-        <v>152.8896528061225</v>
+        <v>151.9813503061225</v>
       </c>
       <c r="O47">
-        <v>53.51137848214286</v>
+        <v>53.19347260714286</v>
       </c>
       <c r="P47">
-        <v>99.3782743239796</v>
+        <v>98.7878776989796</v>
       </c>
       <c r="Q47">
-        <v>103.7782743239796</v>
+        <v>103.1878776989796</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2180758094786325</v>
+        <v>0.2205371629495878</v>
       </c>
       <c r="T47">
-        <v>0.8464551704702594</v>
+        <v>0.8585487161523272</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.740546613199958</v>
+        <v>4.637491252043437</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1356247679927774</v>
+        <v>0.135132590772307</v>
       </c>
       <c r="C48">
-        <v>1421.507146560511</v>
+        <v>1416.904729973688</v>
       </c>
       <c r="D48">
-        <v>2145.857146560511</v>
+        <v>2157.679729973688</v>
       </c>
       <c r="E48">
-        <v>359.0500000000001</v>
+        <v>375.475</v>
       </c>
       <c r="F48">
-        <v>755.5500000000001</v>
+        <v>771.975</v>
       </c>
       <c r="G48">
         <v>31.2</v>
@@ -5217,28 +5217,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M48">
-        <v>41.78191500000001</v>
+        <v>42.6902175</v>
       </c>
       <c r="N48">
-        <v>151.9813503061225</v>
+        <v>151.0730478061225</v>
       </c>
       <c r="O48">
-        <v>53.19347260714286</v>
+        <v>52.87556673214286</v>
       </c>
       <c r="P48">
-        <v>98.7878776989796</v>
+        <v>98.19748107397962</v>
       </c>
       <c r="Q48">
-        <v>103.1878776989796</v>
+        <v>102.5974810739796</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2205371629495878</v>
+        <v>0.223091397683598</v>
       </c>
       <c r="T48">
-        <v>0.8585487161523272</v>
+        <v>0.8710986220488125</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.637491252043437</v>
+        <v>4.538821225404215</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.135132590772307</v>
+        <v>0.1354204135518365</v>
       </c>
       <c r="C49">
-        <v>1416.904729973688</v>
+        <v>1393.550177290288</v>
       </c>
       <c r="D49">
-        <v>2157.679729973688</v>
+        <v>2150.750177290288</v>
       </c>
       <c r="E49">
-        <v>375.475</v>
+        <v>391.9000000000001</v>
       </c>
       <c r="F49">
-        <v>771.975</v>
+        <v>788.4000000000001</v>
       </c>
       <c r="G49">
         <v>31.2</v>
@@ -5299,45 +5299,45 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M49">
-        <v>42.6902175</v>
+        <v>45.56952000000001</v>
       </c>
       <c r="N49">
-        <v>151.0730478061225</v>
+        <v>148.1937453061225</v>
       </c>
       <c r="O49">
-        <v>52.87556673214286</v>
+        <v>51.86781085714286</v>
       </c>
       <c r="P49">
-        <v>98.19748107397962</v>
+        <v>96.3259344489796</v>
       </c>
       <c r="Q49">
-        <v>102.5974810739796</v>
+        <v>100.7259344489796</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.223091397683598</v>
+        <v>0.2257438722150701</v>
       </c>
       <c r="T49">
-        <v>0.8710986220488125</v>
+        <v>0.8841312166336242</v>
       </c>
       <c r="U49">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V49">
         <v>0.35</v>
       </c>
       <c r="W49">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.538821225404215</v>
+        <v>4.252036565364797</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1354204135518365</v>
+        <v>0.134944486331366</v>
       </c>
       <c r="C50">
-        <v>1393.550177290288</v>
+        <v>1388.607665954805</v>
       </c>
       <c r="D50">
-        <v>2150.750177290288</v>
+        <v>2162.232665954805</v>
       </c>
       <c r="E50">
-        <v>391.9</v>
+        <v>408.3249999999999</v>
       </c>
       <c r="F50">
-        <v>788.4</v>
+        <v>804.8249999999999</v>
       </c>
       <c r="G50">
         <v>31.2</v>
@@ -5381,28 +5381,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M50">
-        <v>45.56952</v>
+        <v>46.518885</v>
       </c>
       <c r="N50">
-        <v>148.1937453061225</v>
+        <v>147.2443803061225</v>
       </c>
       <c r="O50">
-        <v>51.86781085714286</v>
+        <v>51.53553310714287</v>
       </c>
       <c r="P50">
-        <v>96.3259344489796</v>
+        <v>95.70884719897961</v>
       </c>
       <c r="Q50">
-        <v>100.7259344489796</v>
+        <v>100.1088471989796</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2257438722150701</v>
+        <v>0.2285003653556196</v>
       </c>
       <c r="T50">
-        <v>0.8841312166336242</v>
+        <v>0.8976748933590166</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.252036565364797</v>
+        <v>4.165260308928782</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.134944486331366</v>
+        <v>0.1344685591108955</v>
       </c>
       <c r="C51">
-        <v>1388.607665954805</v>
+        <v>1383.788418806065</v>
       </c>
       <c r="D51">
-        <v>2162.232665954805</v>
+        <v>2173.838418806065</v>
       </c>
       <c r="E51">
-        <v>408.3249999999999</v>
+        <v>424.75</v>
       </c>
       <c r="F51">
-        <v>804.8249999999999</v>
+        <v>821.25</v>
       </c>
       <c r="G51">
         <v>31.2</v>
@@ -5463,28 +5463,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M51">
-        <v>46.518885</v>
+        <v>47.46825</v>
       </c>
       <c r="N51">
-        <v>147.2443803061225</v>
+        <v>146.2950153061225</v>
       </c>
       <c r="O51">
-        <v>51.53553310714287</v>
+        <v>51.20325535714286</v>
       </c>
       <c r="P51">
-        <v>95.70884719897961</v>
+        <v>95.09175994897959</v>
       </c>
       <c r="Q51">
-        <v>100.1088471989796</v>
+        <v>99.49175994897956</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2285003653556196</v>
+        <v>0.231367118221791</v>
       </c>
       <c r="T51">
-        <v>0.8976748933590166</v>
+        <v>0.9117603171534248</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.165260308928782</v>
+        <v>4.081955102750205</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1344685591108955</v>
+        <v>0.1339926318904251</v>
       </c>
       <c r="C52">
-        <v>1383.788418806065</v>
+        <v>1379.094431411514</v>
       </c>
       <c r="D52">
-        <v>2173.838418806065</v>
+        <v>2185.569431411514</v>
       </c>
       <c r="E52">
-        <v>424.75</v>
+        <v>441.1750000000001</v>
       </c>
       <c r="F52">
-        <v>821.25</v>
+        <v>837.6750000000001</v>
       </c>
       <c r="G52">
         <v>31.2</v>
@@ -5545,28 +5545,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M52">
-        <v>47.46825</v>
+        <v>48.417615</v>
       </c>
       <c r="N52">
-        <v>146.2950153061225</v>
+        <v>145.3456503061225</v>
       </c>
       <c r="O52">
-        <v>51.20325535714286</v>
+        <v>50.87097760714285</v>
       </c>
       <c r="P52">
-        <v>95.09175994897959</v>
+        <v>94.47467269897959</v>
       </c>
       <c r="Q52">
-        <v>99.49175994897956</v>
+        <v>98.87467269897957</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.231367118221791</v>
+        <v>0.2343508814090307</v>
       </c>
       <c r="T52">
-        <v>0.9117603171534248</v>
+        <v>0.9264206562047477</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.081955102750205</v>
+        <v>4.001916767402163</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1339926318904251</v>
+        <v>0.1346997046699546</v>
       </c>
       <c r="C53">
-        <v>1379.094431411514</v>
+        <v>1345.286284206917</v>
       </c>
       <c r="D53">
-        <v>2185.569431411514</v>
+        <v>2168.186284206917</v>
       </c>
       <c r="E53">
-        <v>441.1750000000001</v>
+        <v>457.6</v>
       </c>
       <c r="F53">
-        <v>837.6750000000001</v>
+        <v>854.1</v>
       </c>
       <c r="G53">
         <v>31.2</v>
@@ -5627,45 +5627,45 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M53">
-        <v>48.417615</v>
+        <v>52.35633</v>
       </c>
       <c r="N53">
-        <v>145.3456503061225</v>
+        <v>141.4069353061225</v>
       </c>
       <c r="O53">
-        <v>50.87097760714285</v>
+        <v>49.49242735714287</v>
       </c>
       <c r="P53">
-        <v>94.47467269897959</v>
+        <v>91.9145079489796</v>
       </c>
       <c r="Q53">
-        <v>98.87467269897957</v>
+        <v>96.31450794897958</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2343508814090307</v>
+        <v>0.2374589680624054</v>
       </c>
       <c r="T53">
-        <v>0.9264206562047477</v>
+        <v>0.9416918427165424</v>
       </c>
       <c r="U53">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V53">
         <v>0.35</v>
       </c>
       <c r="W53">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.001916767402163</v>
+        <v>3.700856521190895</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1346997046699546</v>
+        <v>0.1342465274494841</v>
       </c>
       <c r="C54">
-        <v>1345.286284206917</v>
+        <v>1339.97051214467</v>
       </c>
       <c r="D54">
-        <v>2168.186284206917</v>
+        <v>2179.295512144671</v>
       </c>
       <c r="E54">
-        <v>457.6</v>
+        <v>474.0250000000001</v>
       </c>
       <c r="F54">
-        <v>854.1</v>
+        <v>870.5250000000001</v>
       </c>
       <c r="G54">
         <v>31.2</v>
@@ -5709,28 +5709,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M54">
-        <v>52.35633</v>
+        <v>53.36318250000001</v>
       </c>
       <c r="N54">
-        <v>141.4069353061225</v>
+        <v>140.4000828061224</v>
       </c>
       <c r="O54">
-        <v>49.49242735714287</v>
+        <v>49.14002898214285</v>
       </c>
       <c r="P54">
-        <v>91.9145079489796</v>
+        <v>91.26005382397959</v>
       </c>
       <c r="Q54">
-        <v>96.31450794897958</v>
+        <v>95.66005382397957</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2374589680624054</v>
+        <v>0.2406993137223067</v>
       </c>
       <c r="T54">
-        <v>0.9416918427165424</v>
+        <v>0.9576128669522432</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.700856521190895</v>
+        <v>3.63102903965899</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1342465274494841</v>
+        <v>0.1337933502290137</v>
       </c>
       <c r="C55">
-        <v>1339.97051214467</v>
+        <v>1334.769168025565</v>
       </c>
       <c r="D55">
-        <v>2179.295512144671</v>
+        <v>2190.519168025566</v>
       </c>
       <c r="E55">
-        <v>474.0250000000001</v>
+        <v>490.45</v>
       </c>
       <c r="F55">
-        <v>870.5250000000001</v>
+        <v>886.95</v>
       </c>
       <c r="G55">
         <v>31.2</v>
@@ -5791,28 +5791,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M55">
-        <v>53.36318250000001</v>
+        <v>54.370035</v>
       </c>
       <c r="N55">
-        <v>140.4000828061224</v>
+        <v>139.3932303061225</v>
       </c>
       <c r="O55">
-        <v>49.14002898214285</v>
+        <v>48.78763060714286</v>
       </c>
       <c r="P55">
-        <v>91.26005382397959</v>
+        <v>90.6055996989796</v>
       </c>
       <c r="Q55">
-        <v>95.66005382397957</v>
+        <v>95.00559969897958</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2406993137223067</v>
+        <v>0.2440805439761167</v>
       </c>
       <c r="T55">
-        <v>0.9576128669522432</v>
+        <v>0.9742261096329745</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.63102903965899</v>
+        <v>3.563787761146787</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1337933502290137</v>
+        <v>0.1343411730085432</v>
       </c>
       <c r="C56">
-        <v>1334.769168025565</v>
+        <v>1304.790967198594</v>
       </c>
       <c r="D56">
-        <v>2190.519168025566</v>
+        <v>2176.965967198594</v>
       </c>
       <c r="E56">
-        <v>490.45</v>
+        <v>506.8750000000001</v>
       </c>
       <c r="F56">
-        <v>886.95</v>
+        <v>903.3750000000001</v>
       </c>
       <c r="G56">
         <v>31.2</v>
@@ -5873,45 +5873,45 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M56">
-        <v>54.370035</v>
+        <v>57.90633750000001</v>
       </c>
       <c r="N56">
-        <v>139.3932303061225</v>
+        <v>135.8569278061225</v>
       </c>
       <c r="O56">
-        <v>48.78763060714286</v>
+        <v>47.54992473214286</v>
       </c>
       <c r="P56">
-        <v>90.6055996989796</v>
+        <v>88.3070030739796</v>
       </c>
       <c r="Q56">
-        <v>95.00559969897958</v>
+        <v>92.70700307397958</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2440805439761167</v>
+        <v>0.247612051130096</v>
       </c>
       <c r="T56">
-        <v>0.9742261096329745</v>
+        <v>0.9915777186550716</v>
       </c>
       <c r="U56">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V56">
         <v>0.35</v>
       </c>
       <c r="W56">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.563787761146787</v>
+        <v>3.346149552389191</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1343411730085432</v>
+        <v>0.1339061957880728</v>
       </c>
       <c r="C57">
-        <v>1304.790967198594</v>
+        <v>1299.11357236984</v>
       </c>
       <c r="D57">
-        <v>2176.965967198594</v>
+        <v>2187.713572369841</v>
       </c>
       <c r="E57">
-        <v>506.8750000000001</v>
+        <v>523.3000000000001</v>
       </c>
       <c r="F57">
-        <v>903.3750000000001</v>
+        <v>919.8000000000001</v>
       </c>
       <c r="G57">
         <v>31.2</v>
@@ -5955,28 +5955,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M57">
-        <v>57.90633750000001</v>
+        <v>58.95918000000001</v>
       </c>
       <c r="N57">
-        <v>135.8569278061225</v>
+        <v>134.8040853061225</v>
       </c>
       <c r="O57">
-        <v>47.54992473214286</v>
+        <v>47.18142985714286</v>
       </c>
       <c r="P57">
-        <v>88.3070030739796</v>
+        <v>87.6226554489796</v>
       </c>
       <c r="Q57">
-        <v>92.70700307397958</v>
+        <v>92.02265544897958</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.247612051130096</v>
+        <v>0.251304081336529</v>
       </c>
       <c r="T57">
-        <v>0.9915777186550716</v>
+        <v>1.009718037178173</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.346149552389191</v>
+        <v>3.286396881810813</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1339061957880728</v>
+        <v>0.1334712185676022</v>
       </c>
       <c r="C58">
-        <v>1299.11357236984</v>
+        <v>1293.542825161608</v>
       </c>
       <c r="D58">
-        <v>2187.713572369841</v>
+        <v>2198.567825161608</v>
       </c>
       <c r="E58">
-        <v>523.3000000000001</v>
+        <v>539.7250000000001</v>
       </c>
       <c r="F58">
-        <v>919.8000000000001</v>
+        <v>936.2250000000001</v>
       </c>
       <c r="G58">
         <v>31.2</v>
@@ -6037,28 +6037,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M58">
-        <v>58.95918000000001</v>
+        <v>60.01202250000001</v>
       </c>
       <c r="N58">
-        <v>134.8040853061225</v>
+        <v>133.7512428061224</v>
       </c>
       <c r="O58">
-        <v>47.18142985714286</v>
+        <v>46.81293498214285</v>
       </c>
       <c r="P58">
-        <v>87.6226554489796</v>
+        <v>86.93830782397959</v>
       </c>
       <c r="Q58">
-        <v>92.02265544897958</v>
+        <v>91.33830782397956</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.251304081336529</v>
+        <v>0.2551678338781448</v>
       </c>
       <c r="T58">
-        <v>1.009718037178173</v>
+        <v>1.028702091446535</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.286396881810813</v>
+        <v>3.228740796165008</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1334712185676022</v>
+        <v>0.1330362413471318</v>
       </c>
       <c r="C59">
-        <v>1293.542825161608</v>
+        <v>1288.080320872526</v>
       </c>
       <c r="D59">
-        <v>2198.567825161608</v>
+        <v>2209.530320872526</v>
       </c>
       <c r="E59">
-        <v>539.7250000000001</v>
+        <v>556.1500000000001</v>
       </c>
       <c r="F59">
-        <v>936.2250000000001</v>
+        <v>952.6500000000001</v>
       </c>
       <c r="G59">
         <v>31.2</v>
@@ -6119,28 +6119,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M59">
-        <v>60.01202250000001</v>
+        <v>61.06486500000001</v>
       </c>
       <c r="N59">
-        <v>133.7512428061224</v>
+        <v>132.6984003061224</v>
       </c>
       <c r="O59">
-        <v>46.81293498214285</v>
+        <v>46.44444010714285</v>
       </c>
       <c r="P59">
-        <v>86.93830782397959</v>
+        <v>86.25396019897958</v>
       </c>
       <c r="Q59">
-        <v>91.33830782397956</v>
+        <v>90.65396019897956</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2551678338781448</v>
+        <v>0.2592155746360281</v>
       </c>
       <c r="T59">
-        <v>1.028702091446535</v>
+        <v>1.048590148299105</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.228740796165008</v>
+        <v>3.173072851403543</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1330362413471318</v>
+        <v>0.1326012641266613</v>
       </c>
       <c r="C60">
-        <v>1288.080320872526</v>
+        <v>1282.727686778579</v>
       </c>
       <c r="D60">
-        <v>2209.530320872526</v>
+        <v>2220.602686778579</v>
       </c>
       <c r="E60">
-        <v>556.15</v>
+        <v>572.5749999999999</v>
       </c>
       <c r="F60">
-        <v>952.65</v>
+        <v>969.0749999999999</v>
       </c>
       <c r="G60">
         <v>31.2</v>
@@ -6201,28 +6201,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M60">
-        <v>61.064865</v>
+        <v>62.1177075</v>
       </c>
       <c r="N60">
-        <v>132.6984003061225</v>
+        <v>131.6455578061225</v>
       </c>
       <c r="O60">
-        <v>46.44444010714286</v>
+        <v>46.07594523214286</v>
       </c>
       <c r="P60">
-        <v>86.2539601989796</v>
+        <v>85.56961257397961</v>
       </c>
       <c r="Q60">
-        <v>90.65396019897958</v>
+        <v>89.96961257397959</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2592155746360281</v>
+        <v>0.2634607661625886</v>
       </c>
       <c r="T60">
-        <v>1.048590148299105</v>
+        <v>1.069448354266434</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.173072851403544</v>
+        <v>3.119291955617043</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1326012641266613</v>
+        <v>0.1321662869061909</v>
       </c>
       <c r="C61">
-        <v>1282.727686778579</v>
+        <v>1277.486582938354</v>
       </c>
       <c r="D61">
-        <v>2220.602686778579</v>
+        <v>2231.786582938355</v>
       </c>
       <c r="E61">
-        <v>572.5749999999999</v>
+        <v>589</v>
       </c>
       <c r="F61">
-        <v>969.0749999999999</v>
+        <v>985.5</v>
       </c>
       <c r="G61">
         <v>31.2</v>
@@ -6283,28 +6283,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M61">
-        <v>62.1177075</v>
+        <v>63.17055000000001</v>
       </c>
       <c r="N61">
-        <v>131.6455578061225</v>
+        <v>130.5927153061224</v>
       </c>
       <c r="O61">
-        <v>46.07594523214286</v>
+        <v>45.70745035714285</v>
       </c>
       <c r="P61">
-        <v>85.56961257397961</v>
+        <v>84.8852649489796</v>
       </c>
       <c r="Q61">
-        <v>89.96961257397959</v>
+        <v>89.28526494897957</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2634607661625886</v>
+        <v>0.2679182172654772</v>
       </c>
       <c r="T61">
-        <v>1.069448354266434</v>
+        <v>1.09134947053213</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.119291955617043</v>
+        <v>3.067303756356758</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1321662869061909</v>
+        <v>0.1317313096857204</v>
       </c>
       <c r="C62">
-        <v>1277.486582938354</v>
+        <v>1272.358703022759</v>
       </c>
       <c r="D62">
-        <v>2231.786582938355</v>
+        <v>2243.083703022759</v>
       </c>
       <c r="E62">
-        <v>589</v>
+        <v>605.425</v>
       </c>
       <c r="F62">
-        <v>985.5</v>
+        <v>1001.925</v>
       </c>
       <c r="G62">
         <v>31.2</v>
@@ -6365,28 +6365,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M62">
-        <v>63.17055000000001</v>
+        <v>64.2233925</v>
       </c>
       <c r="N62">
-        <v>130.5927153061224</v>
+        <v>129.5398728061224</v>
       </c>
       <c r="O62">
-        <v>45.70745035714285</v>
+        <v>45.33895548214285</v>
       </c>
       <c r="P62">
-        <v>84.8852649489796</v>
+        <v>84.2009173239796</v>
       </c>
       <c r="Q62">
-        <v>89.28526494897957</v>
+        <v>88.60091732397957</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2679182172654772</v>
+        <v>0.2726042556044113</v>
       </c>
       <c r="T62">
-        <v>1.09134947053213</v>
+        <v>1.114373720965297</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.067303756356758</v>
+        <v>3.017020088219763</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1317313096857204</v>
+        <v>0.13443973246525</v>
       </c>
       <c r="C63">
-        <v>1272.358703022759</v>
+        <v>1187.395375698272</v>
       </c>
       <c r="D63">
-        <v>2243.083703022759</v>
+        <v>2174.545375698272</v>
       </c>
       <c r="E63">
-        <v>605.425</v>
+        <v>621.85</v>
       </c>
       <c r="F63">
-        <v>1001.925</v>
+        <v>1018.35</v>
       </c>
       <c r="G63">
         <v>31.2</v>
@@ -6447,45 +6447,45 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M63">
-        <v>64.2233925</v>
+        <v>73.21936500000001</v>
       </c>
       <c r="N63">
-        <v>129.5398728061224</v>
+        <v>120.5439003061225</v>
       </c>
       <c r="O63">
-        <v>45.33895548214285</v>
+        <v>42.19036510714285</v>
       </c>
       <c r="P63">
-        <v>84.2009173239796</v>
+        <v>78.3535351989796</v>
       </c>
       <c r="Q63">
-        <v>88.60091732397957</v>
+        <v>82.75353519897958</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2726042556044113</v>
+        <v>0.2775369275401315</v>
       </c>
       <c r="T63">
-        <v>1.114373720965297</v>
+        <v>1.138609774052842</v>
       </c>
       <c r="U63">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V63">
         <v>0.35</v>
       </c>
       <c r="W63">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>3.017020088219763</v>
+        <v>2.646339056697943</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.13443973246525</v>
+        <v>0.1340554552447795</v>
       </c>
       <c r="C64">
-        <v>1187.395375698272</v>
+        <v>1180.438665793684</v>
       </c>
       <c r="D64">
-        <v>2174.545375698272</v>
+        <v>2184.013665793685</v>
       </c>
       <c r="E64">
-        <v>621.85</v>
+        <v>638.2750000000001</v>
       </c>
       <c r="F64">
-        <v>1018.35</v>
+        <v>1034.775</v>
       </c>
       <c r="G64">
         <v>31.2</v>
@@ -6529,28 +6529,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M64">
-        <v>73.21936500000001</v>
+        <v>74.40032250000002</v>
       </c>
       <c r="N64">
-        <v>120.5439003061225</v>
+        <v>119.3629428061224</v>
       </c>
       <c r="O64">
-        <v>42.19036510714285</v>
+        <v>41.77702998214286</v>
       </c>
       <c r="P64">
-        <v>78.3535351989796</v>
+        <v>77.58591282397958</v>
       </c>
       <c r="Q64">
-        <v>82.75353519897958</v>
+        <v>81.98591282397956</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2775369275401315</v>
+        <v>0.2827362303912959</v>
       </c>
       <c r="T64">
-        <v>1.138609774052842</v>
+        <v>1.164155884064037</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.646339056697943</v>
+        <v>2.604333674845595</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1340554552447795</v>
+        <v>0.133671178024309</v>
       </c>
       <c r="C65">
-        <v>1180.438665793684</v>
+        <v>1173.564769122793</v>
       </c>
       <c r="D65">
-        <v>2184.013665793685</v>
+        <v>2193.564769122794</v>
       </c>
       <c r="E65">
-        <v>638.2750000000001</v>
+        <v>654.7</v>
       </c>
       <c r="F65">
-        <v>1034.775</v>
+        <v>1051.2</v>
       </c>
       <c r="G65">
         <v>31.2</v>
@@ -6611,28 +6611,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M65">
-        <v>74.40032250000002</v>
+        <v>75.58128000000001</v>
       </c>
       <c r="N65">
-        <v>119.3629428061224</v>
+        <v>118.1819853061225</v>
       </c>
       <c r="O65">
-        <v>41.77702998214286</v>
+        <v>41.36369485714286</v>
       </c>
       <c r="P65">
-        <v>77.58591282397958</v>
+        <v>76.8182904489796</v>
       </c>
       <c r="Q65">
-        <v>81.98591282397956</v>
+        <v>81.21829044897957</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2827362303912959</v>
+        <v>0.2882243834008584</v>
       </c>
       <c r="T65">
-        <v>1.164155884064037</v>
+        <v>1.191121222409188</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.604333674845595</v>
+        <v>2.563640961176133</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.133671178024309</v>
+        <v>0.1332869008038385</v>
       </c>
       <c r="C66">
-        <v>1173.564769122793</v>
+        <v>1166.774776931453</v>
       </c>
       <c r="D66">
-        <v>2193.564769122794</v>
+        <v>2203.199776931453</v>
       </c>
       <c r="E66">
-        <v>654.7</v>
+        <v>671.125</v>
       </c>
       <c r="F66">
-        <v>1051.2</v>
+        <v>1067.625</v>
       </c>
       <c r="G66">
         <v>31.2</v>
@@ -6693,28 +6693,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M66">
-        <v>75.58128000000001</v>
+        <v>76.76223750000001</v>
       </c>
       <c r="N66">
-        <v>118.1819853061225</v>
+        <v>117.0010278061225</v>
       </c>
       <c r="O66">
-        <v>41.36369485714286</v>
+        <v>40.95035973214286</v>
       </c>
       <c r="P66">
-        <v>76.8182904489796</v>
+        <v>76.05066807397959</v>
       </c>
       <c r="Q66">
-        <v>81.21829044897957</v>
+        <v>80.45066807397957</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2882243834008584</v>
+        <v>0.2940261451538244</v>
       </c>
       <c r="T66">
-        <v>1.191121222409188</v>
+        <v>1.219627437231205</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.563640961176133</v>
+        <v>2.524200331004192</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1332869008038385</v>
+        <v>0.1345757235833681</v>
       </c>
       <c r="C67">
-        <v>1166.774776931453</v>
+        <v>1118.364297728943</v>
       </c>
       <c r="D67">
-        <v>2203.199776931453</v>
+        <v>2171.214297728943</v>
       </c>
       <c r="E67">
-        <v>671.125</v>
+        <v>687.55</v>
       </c>
       <c r="F67">
-        <v>1067.625</v>
+        <v>1084.05</v>
       </c>
       <c r="G67">
         <v>31.2</v>
@@ -6775,45 +6775,45 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M67">
-        <v>76.76223750000001</v>
+        <v>82.17099</v>
       </c>
       <c r="N67">
-        <v>117.0010278061225</v>
+        <v>111.5922753061225</v>
       </c>
       <c r="O67">
-        <v>40.95035973214286</v>
+        <v>39.05729635714286</v>
       </c>
       <c r="P67">
-        <v>76.05066807397959</v>
+        <v>72.5349789489796</v>
       </c>
       <c r="Q67">
-        <v>80.45066807397957</v>
+        <v>76.93497894897958</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2940261451538244</v>
+        <v>0.3001691870099061</v>
       </c>
       <c r="T67">
-        <v>1.219627437231205</v>
+        <v>1.249810488219222</v>
       </c>
       <c r="U67">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V67">
         <v>0.35</v>
       </c>
       <c r="W67">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.524200331004192</v>
+        <v>2.358049541646297</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1345757235833681</v>
+        <v>0.1342167963628976</v>
       </c>
       <c r="C68">
-        <v>1118.364297728943</v>
+        <v>1110.753323400388</v>
       </c>
       <c r="D68">
-        <v>2171.214297728943</v>
+        <v>2180.028323400388</v>
       </c>
       <c r="E68">
-        <v>687.55</v>
+        <v>703.9750000000001</v>
       </c>
       <c r="F68">
-        <v>1084.05</v>
+        <v>1100.475</v>
       </c>
       <c r="G68">
         <v>31.2</v>
@@ -6857,28 +6857,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M68">
-        <v>82.17099</v>
+        <v>83.41600500000001</v>
       </c>
       <c r="N68">
-        <v>111.5922753061225</v>
+        <v>110.3472603061225</v>
       </c>
       <c r="O68">
-        <v>39.05729635714286</v>
+        <v>38.62154110714285</v>
       </c>
       <c r="P68">
-        <v>72.5349789489796</v>
+        <v>71.72571919897959</v>
       </c>
       <c r="Q68">
-        <v>76.93497894897958</v>
+        <v>76.12571919897957</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3001691870099061</v>
+        <v>0.3066845344330232</v>
       </c>
       <c r="T68">
-        <v>1.249810488219222</v>
+        <v>1.281822815024696</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.358049541646297</v>
+        <v>2.322854772367994</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1342167963628976</v>
+        <v>0.1338578691424271</v>
       </c>
       <c r="C69">
-        <v>1110.753323400388</v>
+        <v>1103.214201678903</v>
       </c>
       <c r="D69">
-        <v>2180.028323400388</v>
+        <v>2188.914201678903</v>
       </c>
       <c r="E69">
-        <v>703.9750000000001</v>
+        <v>720.4000000000001</v>
       </c>
       <c r="F69">
-        <v>1100.475</v>
+        <v>1116.9</v>
       </c>
       <c r="G69">
         <v>31.2</v>
@@ -6939,28 +6939,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M69">
-        <v>83.41600500000001</v>
+        <v>84.66102000000001</v>
       </c>
       <c r="N69">
-        <v>110.3472603061225</v>
+        <v>109.1022453061225</v>
       </c>
       <c r="O69">
-        <v>38.62154110714285</v>
+        <v>38.18578585714285</v>
       </c>
       <c r="P69">
-        <v>71.72571919897959</v>
+        <v>70.91645944897959</v>
       </c>
       <c r="Q69">
-        <v>76.12571919897957</v>
+        <v>75.31645944897957</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3066845344330232</v>
+        <v>0.3136070910700849</v>
       </c>
       <c r="T69">
-        <v>1.281822815024696</v>
+        <v>1.315835912255511</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.322854772367994</v>
+        <v>2.288695143362582</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1338578691424271</v>
+        <v>0.1334989419219567</v>
       </c>
       <c r="C70">
-        <v>1103.214201678903</v>
+        <v>1095.74781478231</v>
       </c>
       <c r="D70">
-        <v>2188.914201678903</v>
+        <v>2197.87281478231</v>
       </c>
       <c r="E70">
-        <v>720.4000000000001</v>
+        <v>736.825</v>
       </c>
       <c r="F70">
-        <v>1116.9</v>
+        <v>1133.325</v>
       </c>
       <c r="G70">
         <v>31.2</v>
@@ -7021,28 +7021,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M70">
-        <v>84.66102000000001</v>
+        <v>85.90603500000002</v>
       </c>
       <c r="N70">
-        <v>109.1022453061225</v>
+        <v>107.8572303061224</v>
       </c>
       <c r="O70">
-        <v>38.18578585714285</v>
+        <v>37.75003060714285</v>
       </c>
       <c r="P70">
-        <v>70.91645944897959</v>
+        <v>70.1071996989796</v>
       </c>
       <c r="Q70">
-        <v>75.31645944897957</v>
+        <v>74.50719969897958</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3136070910700849</v>
+        <v>0.3209762642643764</v>
       </c>
       <c r="T70">
-        <v>1.315835912255511</v>
+        <v>1.352043402856056</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.288695143362582</v>
+        <v>2.25552564853124</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1334989419219567</v>
+        <v>0.1331400147014862</v>
       </c>
       <c r="C71">
-        <v>1095.74781478231</v>
+        <v>1088.355059430466</v>
       </c>
       <c r="D71">
-        <v>2197.87281478231</v>
+        <v>2206.905059430466</v>
       </c>
       <c r="E71">
-        <v>736.825</v>
+        <v>753.25</v>
       </c>
       <c r="F71">
-        <v>1133.325</v>
+        <v>1149.75</v>
       </c>
       <c r="G71">
         <v>31.2</v>
@@ -7103,28 +7103,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M71">
-        <v>85.90603500000002</v>
+        <v>87.15105000000001</v>
       </c>
       <c r="N71">
-        <v>107.8572303061224</v>
+        <v>106.6122153061225</v>
       </c>
       <c r="O71">
-        <v>37.75003060714285</v>
+        <v>37.31427535714285</v>
       </c>
       <c r="P71">
-        <v>70.1071996989796</v>
+        <v>69.2979399489796</v>
       </c>
       <c r="Q71">
-        <v>74.50719969897958</v>
+        <v>73.69793994897958</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3209762642643764</v>
+        <v>0.3288367156716208</v>
       </c>
       <c r="T71">
-        <v>1.352043402856056</v>
+        <v>1.390664726163305</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.25552564853124</v>
+        <v>2.223303853552223</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1331400147014862</v>
+        <v>0.1327810874810158</v>
       </c>
       <c r="C72">
-        <v>1088.355059430466</v>
+        <v>1081.036847144478</v>
       </c>
       <c r="D72">
-        <v>2206.905059430466</v>
+        <v>2216.011847144478</v>
       </c>
       <c r="E72">
-        <v>753.25</v>
+        <v>769.6750000000002</v>
       </c>
       <c r="F72">
-        <v>1149.75</v>
+        <v>1166.175</v>
       </c>
       <c r="G72">
         <v>31.2</v>
@@ -7185,28 +7185,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M72">
-        <v>87.15105000000001</v>
+        <v>88.39606500000002</v>
       </c>
       <c r="N72">
-        <v>106.6122153061225</v>
+        <v>105.3672003061224</v>
       </c>
       <c r="O72">
-        <v>37.31427535714285</v>
+        <v>36.87852010714285</v>
       </c>
       <c r="P72">
-        <v>69.2979399489796</v>
+        <v>68.48868019897958</v>
       </c>
       <c r="Q72">
-        <v>73.69793994897958</v>
+        <v>72.88868019897956</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3288367156716208</v>
+        <v>0.3372392671759165</v>
       </c>
       <c r="T72">
-        <v>1.390664726163305</v>
+        <v>1.431949589008984</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.223303853552223</v>
+        <v>2.191989714769797</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1327810874810157</v>
+        <v>0.1324221602605453</v>
       </c>
       <c r="C73">
-        <v>1081.036847144479</v>
+        <v>1073.794104553355</v>
       </c>
       <c r="D73">
-        <v>2216.011847144479</v>
+        <v>2225.194104553355</v>
       </c>
       <c r="E73">
-        <v>769.675</v>
+        <v>786.0999999999999</v>
       </c>
       <c r="F73">
-        <v>1166.175</v>
+        <v>1182.6</v>
       </c>
       <c r="G73">
         <v>31.2</v>
@@ -7267,28 +7267,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M73">
-        <v>88.39606500000001</v>
+        <v>89.64108</v>
       </c>
       <c r="N73">
-        <v>105.3672003061225</v>
+        <v>104.1221853061225</v>
       </c>
       <c r="O73">
-        <v>36.87852010714285</v>
+        <v>36.44276485714286</v>
       </c>
       <c r="P73">
-        <v>68.48868019897961</v>
+        <v>67.6794204489796</v>
       </c>
       <c r="Q73">
-        <v>72.88868019897959</v>
+        <v>72.07942044897958</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3372392671759163</v>
+        <v>0.3462420009305188</v>
       </c>
       <c r="T73">
-        <v>1.431949589008984</v>
+        <v>1.476183370629354</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.191989714769797</v>
+        <v>2.161545413175772</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1324221602605453</v>
+        <v>0.1320632330400748</v>
       </c>
       <c r="C74">
-        <v>1073.794104553355</v>
+        <v>1066.627773708307</v>
       </c>
       <c r="D74">
-        <v>2225.194104553355</v>
+        <v>2234.452773708307</v>
       </c>
       <c r="E74">
-        <v>786.0999999999999</v>
+        <v>802.5249999999999</v>
       </c>
       <c r="F74">
-        <v>1182.6</v>
+        <v>1199.025</v>
       </c>
       <c r="G74">
         <v>31.2</v>
@@ -7349,28 +7349,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M74">
-        <v>89.64108</v>
+        <v>90.886095</v>
       </c>
       <c r="N74">
-        <v>104.1221853061225</v>
+        <v>102.8771703061225</v>
       </c>
       <c r="O74">
-        <v>36.44276485714286</v>
+        <v>36.00700960714286</v>
       </c>
       <c r="P74">
-        <v>67.6794204489796</v>
+        <v>66.8701606989796</v>
       </c>
       <c r="Q74">
-        <v>72.07942044897958</v>
+        <v>71.27016069897958</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3462420009305188</v>
+        <v>0.3559116038521289</v>
       </c>
       <c r="T74">
-        <v>1.476183370629354</v>
+        <v>1.523693728666049</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.161545413175772</v>
+        <v>2.131935202036378</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1320632330400748</v>
+        <v>0.1317043058196044</v>
       </c>
       <c r="C75">
-        <v>1066.627773708307</v>
+        <v>1059.538812404945</v>
       </c>
       <c r="D75">
-        <v>2234.452773708307</v>
+        <v>2243.788812404945</v>
       </c>
       <c r="E75">
-        <v>802.5249999999999</v>
+        <v>818.95</v>
       </c>
       <c r="F75">
-        <v>1199.025</v>
+        <v>1215.45</v>
       </c>
       <c r="G75">
         <v>31.2</v>
@@ -7431,28 +7431,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M75">
-        <v>90.886095</v>
+        <v>92.13111000000001</v>
       </c>
       <c r="N75">
-        <v>102.8771703061225</v>
+        <v>101.6321553061225</v>
       </c>
       <c r="O75">
-        <v>36.00700960714286</v>
+        <v>35.57125435714286</v>
       </c>
       <c r="P75">
-        <v>66.8701606989796</v>
+        <v>66.06090094897959</v>
       </c>
       <c r="Q75">
-        <v>71.27016069897958</v>
+        <v>70.46090094897957</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3559116038521289</v>
+        <v>0.3663250223830936</v>
       </c>
       <c r="T75">
-        <v>1.523693728666049</v>
+        <v>1.574858729628643</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.131935202036378</v>
+        <v>2.103125266873724</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1317043058196044</v>
+        <v>0.1313453785991339</v>
       </c>
       <c r="C76">
-        <v>1059.538812404945</v>
+        <v>1052.528194513569</v>
       </c>
       <c r="D76">
-        <v>2243.788812404945</v>
+        <v>2253.20319451357</v>
       </c>
       <c r="E76">
-        <v>818.95</v>
+        <v>835.375</v>
       </c>
       <c r="F76">
-        <v>1215.45</v>
+        <v>1231.875</v>
       </c>
       <c r="G76">
         <v>31.2</v>
@@ -7513,28 +7513,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M76">
-        <v>92.13111000000001</v>
+        <v>93.376125</v>
       </c>
       <c r="N76">
-        <v>101.6321553061225</v>
+        <v>100.3871403061225</v>
       </c>
       <c r="O76">
-        <v>35.57125435714286</v>
+        <v>35.13549910714286</v>
       </c>
       <c r="P76">
-        <v>66.06090094897959</v>
+        <v>65.2516411989796</v>
       </c>
       <c r="Q76">
-        <v>70.46090094897957</v>
+        <v>69.65164119897958</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3663250223830936</v>
+        <v>0.3775715143965356</v>
       </c>
       <c r="T76">
-        <v>1.574858729628643</v>
+        <v>1.630116930668245</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.103125266873724</v>
+        <v>2.075083596648741</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1313453785991339</v>
+        <v>0.1309864513786634</v>
       </c>
       <c r="C77">
-        <v>1052.528194513569</v>
+        <v>1045.596910317823</v>
       </c>
       <c r="D77">
-        <v>2253.20319451357</v>
+        <v>2262.696910317823</v>
       </c>
       <c r="E77">
-        <v>835.375</v>
+        <v>851.8</v>
       </c>
       <c r="F77">
-        <v>1231.875</v>
+        <v>1248.3</v>
       </c>
       <c r="G77">
         <v>31.2</v>
@@ -7595,28 +7595,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M77">
-        <v>93.376125</v>
+        <v>94.62114000000001</v>
       </c>
       <c r="N77">
-        <v>100.3871403061225</v>
+        <v>99.14212530612245</v>
       </c>
       <c r="O77">
-        <v>35.13549910714286</v>
+        <v>34.69974385714286</v>
       </c>
       <c r="P77">
-        <v>65.2516411989796</v>
+        <v>64.4423814489796</v>
       </c>
       <c r="Q77">
-        <v>69.65164119897958</v>
+        <v>68.84238144897958</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3775715143965356</v>
+        <v>0.3897552140777643</v>
       </c>
       <c r="T77">
-        <v>1.630116930668245</v>
+        <v>1.68997998179448</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.075083596648741</v>
+        <v>2.047779865113889</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1309864513786634</v>
+        <v>0.130627524158193</v>
       </c>
       <c r="C78">
-        <v>1045.596910317823</v>
+        <v>1038.745966861935</v>
       </c>
       <c r="D78">
-        <v>2262.696910317823</v>
+        <v>2272.270966861935</v>
       </c>
       <c r="E78">
-        <v>851.8</v>
+        <v>868.2250000000001</v>
       </c>
       <c r="F78">
-        <v>1248.3</v>
+        <v>1264.725</v>
       </c>
       <c r="G78">
         <v>31.2</v>
@@ -7677,28 +7677,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M78">
-        <v>94.62114000000001</v>
+        <v>95.86615500000002</v>
       </c>
       <c r="N78">
-        <v>99.14212530612245</v>
+        <v>97.89711030612244</v>
       </c>
       <c r="O78">
-        <v>34.69974385714286</v>
+        <v>34.26398860714285</v>
       </c>
       <c r="P78">
-        <v>64.4423814489796</v>
+        <v>63.63312169897959</v>
       </c>
       <c r="Q78">
-        <v>68.84238144897958</v>
+        <v>68.03312169897957</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3897552140777643</v>
+        <v>0.4029983659051868</v>
       </c>
       <c r="T78">
-        <v>1.68997998179448</v>
+        <v>1.755048515627344</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.047779865113889</v>
+        <v>2.021185321411111</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.130627524158193</v>
+        <v>0.1374679969377225</v>
       </c>
       <c r="C79">
-        <v>1038.745966861935</v>
+        <v>852.7589799550515</v>
       </c>
       <c r="D79">
-        <v>2272.270966861935</v>
+        <v>2102.708979955052</v>
       </c>
       <c r="E79">
-        <v>868.2250000000001</v>
+        <v>884.6500000000001</v>
       </c>
       <c r="F79">
-        <v>1264.725</v>
+        <v>1281.15</v>
       </c>
       <c r="G79">
         <v>31.2</v>
@@ -7759,45 +7759,45 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M79">
-        <v>95.86615500000002</v>
+        <v>115.3035</v>
       </c>
       <c r="N79">
-        <v>97.89711030612244</v>
+        <v>78.45976530612246</v>
       </c>
       <c r="O79">
-        <v>34.26398860714285</v>
+        <v>27.46091785714286</v>
       </c>
       <c r="P79">
-        <v>63.63312169897959</v>
+        <v>50.9988474489796</v>
       </c>
       <c r="Q79">
-        <v>68.03312169897957</v>
+        <v>55.39884744897958</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4029983659051868</v>
+        <v>0.4174454406260114</v>
       </c>
       <c r="T79">
-        <v>1.755048515627344</v>
+        <v>1.826032370717741</v>
       </c>
       <c r="U79">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V79">
         <v>0.35</v>
       </c>
       <c r="W79">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.021185321411111</v>
+        <v>1.680462998140754</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1374679969377225</v>
+        <v>0.137201369717252</v>
       </c>
       <c r="C80">
-        <v>852.7589799550515</v>
+        <v>842.4677988739365</v>
       </c>
       <c r="D80">
-        <v>2102.708979955052</v>
+        <v>2108.842798873937</v>
       </c>
       <c r="E80">
-        <v>884.6500000000001</v>
+        <v>901.075</v>
       </c>
       <c r="F80">
-        <v>1281.15</v>
+        <v>1297.575</v>
       </c>
       <c r="G80">
         <v>31.2</v>
@@ -7841,28 +7841,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M80">
-        <v>115.3035</v>
+        <v>116.78175</v>
       </c>
       <c r="N80">
-        <v>78.45976530612246</v>
+        <v>76.98151530612246</v>
       </c>
       <c r="O80">
-        <v>27.46091785714286</v>
+        <v>26.94353035714286</v>
       </c>
       <c r="P80">
-        <v>50.9988474489796</v>
+        <v>50.0379849489796</v>
       </c>
       <c r="Q80">
-        <v>55.39884744897958</v>
+        <v>54.43798494897958</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4174454406260114</v>
+        <v>0.4332684272250097</v>
       </c>
       <c r="T80">
-        <v>1.826032370717741</v>
+        <v>1.903776592959605</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.680462998140754</v>
+        <v>1.659191314619985</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.137201369717252</v>
+        <v>0.1369347424967816</v>
       </c>
       <c r="C81">
-        <v>842.4677988739365</v>
+        <v>832.2125084541531</v>
       </c>
       <c r="D81">
-        <v>2108.842798873937</v>
+        <v>2115.012508454153</v>
       </c>
       <c r="E81">
-        <v>901.075</v>
+        <v>917.5</v>
       </c>
       <c r="F81">
-        <v>1297.575</v>
+        <v>1314</v>
       </c>
       <c r="G81">
         <v>31.2</v>
@@ -7923,28 +7923,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M81">
-        <v>116.78175</v>
+        <v>118.26</v>
       </c>
       <c r="N81">
-        <v>76.98151530612246</v>
+        <v>75.50326530612247</v>
       </c>
       <c r="O81">
-        <v>26.94353035714286</v>
+        <v>26.42614285714286</v>
       </c>
       <c r="P81">
-        <v>50.0379849489796</v>
+        <v>49.07712244897961</v>
       </c>
       <c r="Q81">
-        <v>54.43798494897958</v>
+        <v>53.47712244897959</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4332684272250097</v>
+        <v>0.4506737124839079</v>
       </c>
       <c r="T81">
-        <v>1.903776592959605</v>
+        <v>1.989295237425655</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.659191314619985</v>
+        <v>1.638451423187236</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1369347424967816</v>
+        <v>0.1366681152763111</v>
       </c>
       <c r="C82">
-        <v>832.2125084541531</v>
+        <v>821.9934246292009</v>
       </c>
       <c r="D82">
-        <v>2115.012508454153</v>
+        <v>2121.218424629201</v>
       </c>
       <c r="E82">
-        <v>917.5</v>
+        <v>933.9250000000002</v>
       </c>
       <c r="F82">
-        <v>1314</v>
+        <v>1330.425</v>
       </c>
       <c r="G82">
         <v>31.2</v>
@@ -8005,28 +8005,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M82">
-        <v>118.26</v>
+        <v>119.73825</v>
       </c>
       <c r="N82">
-        <v>75.50326530612247</v>
+        <v>74.02501530612246</v>
       </c>
       <c r="O82">
-        <v>26.42614285714286</v>
+        <v>25.90875535714286</v>
       </c>
       <c r="P82">
-        <v>49.07712244897961</v>
+        <v>48.1162599489796</v>
       </c>
       <c r="Q82">
-        <v>53.47712244897959</v>
+        <v>52.51625994897957</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4506737124839079</v>
+        <v>0.4699111330332164</v>
       </c>
       <c r="T82">
-        <v>1.989295237425655</v>
+        <v>2.083815844467078</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.638451423187236</v>
+        <v>1.618223627839245</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1366681152763111</v>
+        <v>0.1364014880558406</v>
       </c>
       <c r="C83">
-        <v>821.9934246292009</v>
+        <v>811.8108670515705</v>
       </c>
       <c r="D83">
-        <v>2121.218424629201</v>
+        <v>2127.460867051571</v>
       </c>
       <c r="E83">
-        <v>933.9250000000002</v>
+        <v>950.3500000000001</v>
       </c>
       <c r="F83">
-        <v>1330.425</v>
+        <v>1346.85</v>
       </c>
       <c r="G83">
         <v>31.2</v>
@@ -8087,28 +8087,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M83">
-        <v>119.73825</v>
+        <v>121.2165</v>
       </c>
       <c r="N83">
-        <v>74.02501530612246</v>
+        <v>72.54676530612245</v>
       </c>
       <c r="O83">
-        <v>25.90875535714286</v>
+        <v>25.39136785714286</v>
       </c>
       <c r="P83">
-        <v>48.1162599489796</v>
+        <v>47.1553974489796</v>
       </c>
       <c r="Q83">
-        <v>52.51625994897957</v>
+        <v>51.55539744897958</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4699111330332164</v>
+        <v>0.4912860447546702</v>
       </c>
       <c r="T83">
-        <v>2.083815844467078</v>
+        <v>2.188838741179771</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.618223627839245</v>
+        <v>1.5984891933534</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1364014880558406</v>
+        <v>0.1361348608353702</v>
       </c>
       <c r="C84">
-        <v>811.8108670515705</v>
+        <v>801.6651591476239</v>
       </c>
       <c r="D84">
-        <v>2127.460867051571</v>
+        <v>2133.740159147624</v>
       </c>
       <c r="E84">
-        <v>950.3500000000001</v>
+        <v>966.7750000000001</v>
       </c>
       <c r="F84">
-        <v>1346.85</v>
+        <v>1363.275</v>
       </c>
       <c r="G84">
         <v>31.2</v>
@@ -8169,28 +8169,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M84">
-        <v>121.2165</v>
+        <v>122.69475</v>
       </c>
       <c r="N84">
-        <v>72.54676530612245</v>
+        <v>71.06851530612246</v>
       </c>
       <c r="O84">
-        <v>25.39136785714286</v>
+        <v>24.87398035714286</v>
       </c>
       <c r="P84">
-        <v>47.1553974489796</v>
+        <v>46.1945349489796</v>
       </c>
       <c r="Q84">
-        <v>51.55539744897958</v>
+        <v>50.59453494897958</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4912860447546702</v>
+        <v>0.5151756519727659</v>
       </c>
       <c r="T84">
-        <v>2.188838741179771</v>
+        <v>2.306217272799841</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.5984891933534</v>
+        <v>1.579230287409384</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1361348608353702</v>
+        <v>0.1358682336148997</v>
       </c>
       <c r="C85">
-        <v>801.6651591476239</v>
+        <v>791.5566281734548</v>
       </c>
       <c r="D85">
-        <v>2133.740159147624</v>
+        <v>2140.056628173455</v>
       </c>
       <c r="E85">
-        <v>966.7750000000001</v>
+        <v>983.2</v>
       </c>
       <c r="F85">
-        <v>1363.275</v>
+        <v>1379.7</v>
       </c>
       <c r="G85">
         <v>31.2</v>
@@ -8251,28 +8251,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M85">
-        <v>122.69475</v>
+        <v>124.173</v>
       </c>
       <c r="N85">
-        <v>71.06851530612246</v>
+        <v>69.59026530612246</v>
       </c>
       <c r="O85">
-        <v>24.87398035714286</v>
+        <v>24.35659285714286</v>
       </c>
       <c r="P85">
-        <v>46.1945349489796</v>
+        <v>45.2336724489796</v>
       </c>
       <c r="Q85">
-        <v>50.59453494897958</v>
+        <v>49.63367244897958</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5151756519727659</v>
+        <v>0.5420514600931233</v>
       </c>
       <c r="T85">
-        <v>2.306217272799841</v>
+        <v>2.438268120872418</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.579230287409384</v>
+        <v>1.560429926844986</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1358682336148997</v>
+        <v>0.1356016063944292</v>
       </c>
       <c r="C86">
-        <v>791.5566281734548</v>
+        <v>781.4856052717382</v>
       </c>
       <c r="D86">
-        <v>2140.056628173455</v>
+        <v>2146.410605271738</v>
       </c>
       <c r="E86">
-        <v>983.2</v>
+        <v>999.625</v>
       </c>
       <c r="F86">
-        <v>1379.7</v>
+        <v>1396.125</v>
       </c>
       <c r="G86">
         <v>31.2</v>
@@ -8333,28 +8333,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M86">
-        <v>124.173</v>
+        <v>125.65125</v>
       </c>
       <c r="N86">
-        <v>69.59026530612246</v>
+        <v>68.11201530612247</v>
       </c>
       <c r="O86">
-        <v>24.35659285714286</v>
+        <v>23.83920535714286</v>
       </c>
       <c r="P86">
-        <v>45.2336724489796</v>
+        <v>44.27280994897961</v>
       </c>
       <c r="Q86">
-        <v>49.63367244897958</v>
+        <v>48.67280994897959</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.542051460093123</v>
+        <v>0.5725107092961947</v>
       </c>
       <c r="T86">
-        <v>2.438268120872416</v>
+        <v>2.587925748688004</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.560429926844986</v>
+        <v>1.542071927705634</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1356016063944292</v>
+        <v>0.1353349791739588</v>
       </c>
       <c r="C87">
-        <v>781.4856052717382</v>
+        <v>771.4524255296071</v>
       </c>
       <c r="D87">
-        <v>2146.410605271738</v>
+        <v>2152.802425529607</v>
       </c>
       <c r="E87">
-        <v>999.625</v>
+        <v>1016.05</v>
       </c>
       <c r="F87">
-        <v>1396.125</v>
+        <v>1412.55</v>
       </c>
       <c r="G87">
         <v>31.2</v>
@@ -8415,28 +8415,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M87">
-        <v>125.65125</v>
+        <v>127.1295</v>
       </c>
       <c r="N87">
-        <v>68.11201530612247</v>
+        <v>66.63376530612247</v>
       </c>
       <c r="O87">
-        <v>23.83920535714286</v>
+        <v>23.32181785714286</v>
       </c>
       <c r="P87">
-        <v>44.27280994897961</v>
+        <v>43.31194744897961</v>
       </c>
       <c r="Q87">
-        <v>48.67280994897959</v>
+        <v>47.71194744897959</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5725107092961947</v>
+        <v>0.6073212798139911</v>
       </c>
       <c r="T87">
-        <v>2.587925748688004</v>
+        <v>2.758963037620104</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.542071927705634</v>
+        <v>1.524140858778824</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1353349791739588</v>
+        <v>0.1350683519534883</v>
       </c>
       <c r="C88">
-        <v>771.4524255296071</v>
+        <v>761.4574280375523</v>
       </c>
       <c r="D88">
-        <v>2152.802425529607</v>
+        <v>2159.232428037552</v>
       </c>
       <c r="E88">
-        <v>1016.05</v>
+        <v>1032.475</v>
       </c>
       <c r="F88">
-        <v>1412.55</v>
+        <v>1428.975</v>
       </c>
       <c r="G88">
         <v>31.2</v>
@@ -8497,28 +8497,28 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M88">
-        <v>127.1295</v>
+        <v>128.60775</v>
       </c>
       <c r="N88">
-        <v>66.63376530612247</v>
+        <v>65.15551530612248</v>
       </c>
       <c r="O88">
-        <v>23.32181785714286</v>
+        <v>22.80443035714287</v>
       </c>
       <c r="P88">
-        <v>43.31194744897961</v>
+        <v>42.35108494897962</v>
       </c>
       <c r="Q88">
-        <v>47.71194744897959</v>
+        <v>46.7510849489796</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6073212798139911</v>
+        <v>0.6474873227191406</v>
       </c>
       <c r="T88">
-        <v>2.758963037620104</v>
+        <v>2.95631375561868</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.524140858778824</v>
+        <v>1.50662199833309</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1350683519534883</v>
+        <v>0.1742240548081624</v>
       </c>
       <c r="C89">
-        <v>761.4574280375523</v>
+        <v>86.69576772333994</v>
       </c>
       <c r="D89">
-        <v>2159.232428037552</v>
+        <v>1500.89576772334</v>
       </c>
       <c r="E89">
-        <v>1032.475</v>
+        <v>1048.9</v>
       </c>
       <c r="F89">
-        <v>1428.975</v>
+        <v>1445.4</v>
       </c>
       <c r="G89">
         <v>31.2</v>
@@ -8579,45 +8579,45 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M89">
-        <v>128.60775</v>
+        <v>212.18472</v>
       </c>
       <c r="N89">
-        <v>65.15551530612248</v>
+        <v>-18.42145469387756</v>
       </c>
       <c r="O89">
-        <v>22.80443035714287</v>
+        <v>-6.447509142857147</v>
       </c>
       <c r="P89">
-        <v>42.35108494897962</v>
+        <v>-11.97394555102042</v>
       </c>
       <c r="Q89">
-        <v>46.7510849489796</v>
+        <v>-7.57394555102044</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6474873227191406</v>
+        <v>0.7194085889373397</v>
       </c>
       <c r="T89">
-        <v>2.95631375561868</v>
+        <v>3.309689704577512</v>
       </c>
       <c r="U89">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.35</v>
+        <v>0.3196136972405122</v>
       </c>
       <c r="W89">
-        <v>0.0585</v>
+        <v>0.09988070924509283</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.50662199833309</v>
+        <v>0.9131819921157491</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1742240548081624</v>
+        <v>0.1752340548081624</v>
       </c>
       <c r="C90">
-        <v>86.69576772333994</v>
+        <v>58.55897574056303</v>
       </c>
       <c r="D90">
-        <v>1500.89576772334</v>
+        <v>1489.183975740563</v>
       </c>
       <c r="E90">
-        <v>1048.9</v>
+        <v>1065.325</v>
       </c>
       <c r="F90">
-        <v>1445.4</v>
+        <v>1461.825</v>
       </c>
       <c r="G90">
         <v>31.2</v>
@@ -8661,37 +8661,37 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M90">
-        <v>212.18472</v>
+        <v>214.59591</v>
       </c>
       <c r="N90">
-        <v>-18.42145469387756</v>
+        <v>-20.83264469387757</v>
       </c>
       <c r="O90">
-        <v>-6.447509142857147</v>
+        <v>-7.291425642857148</v>
       </c>
       <c r="P90">
-        <v>-11.97394555102042</v>
+        <v>-13.54121905102042</v>
       </c>
       <c r="Q90">
-        <v>-7.57394555102044</v>
+        <v>-9.141219051020443</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7194085889373397</v>
+        <v>0.7806457333861888</v>
       </c>
       <c r="T90">
-        <v>3.309689704577512</v>
+        <v>3.610570586811831</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.3196136972405122</v>
+        <v>0.3160225321029784</v>
       </c>
       <c r="W90">
-        <v>0.09988070924509283</v>
+        <v>0.1004078922872828</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9131819921157491</v>
+        <v>0.9029215202942238</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1752340548081624</v>
+        <v>0.1762440548081624</v>
       </c>
       <c r="C91">
-        <v>58.55897574056303</v>
+        <v>30.60354748371446</v>
       </c>
       <c r="D91">
-        <v>1489.183975740563</v>
+        <v>1477.653547483714</v>
       </c>
       <c r="E91">
-        <v>1065.325</v>
+        <v>1081.75</v>
       </c>
       <c r="F91">
-        <v>1461.825</v>
+        <v>1478.25</v>
       </c>
       <c r="G91">
         <v>31.2</v>
@@ -8743,37 +8743,37 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M91">
-        <v>214.59591</v>
+        <v>217.0071</v>
       </c>
       <c r="N91">
-        <v>-20.83264469387757</v>
+        <v>-23.24383469387755</v>
       </c>
       <c r="O91">
-        <v>-7.291425642857148</v>
+        <v>-8.135342142857141</v>
       </c>
       <c r="P91">
-        <v>-13.54121905102042</v>
+        <v>-15.1084925510204</v>
       </c>
       <c r="Q91">
-        <v>-9.141219051020443</v>
+        <v>-10.70849255102043</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7806457333861888</v>
+        <v>0.8541303067248077</v>
       </c>
       <c r="T91">
-        <v>3.610570586811831</v>
+        <v>3.971627645493014</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.3160225321029784</v>
+        <v>0.3125111706351675</v>
       </c>
       <c r="W91">
-        <v>0.1004078922872828</v>
+        <v>0.1009233601507574</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9029215202942238</v>
+        <v>0.8928890589576215</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1762440548081624</v>
+        <v>0.1772540548081624</v>
       </c>
       <c r="C92">
-        <v>30.60354748371446</v>
+        <v>2.825302540935127</v>
       </c>
       <c r="D92">
-        <v>1477.653547483714</v>
+        <v>1466.300302540935</v>
       </c>
       <c r="E92">
-        <v>1081.75</v>
+        <v>1098.175</v>
       </c>
       <c r="F92">
-        <v>1478.25</v>
+        <v>1494.675</v>
       </c>
       <c r="G92">
         <v>31.2</v>
@@ -8825,37 +8825,37 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M92">
-        <v>217.0071</v>
+        <v>219.41829</v>
       </c>
       <c r="N92">
-        <v>-23.24383469387755</v>
+        <v>-25.65502469387755</v>
       </c>
       <c r="O92">
-        <v>-8.135342142857141</v>
+        <v>-8.979258642857141</v>
       </c>
       <c r="P92">
-        <v>-15.1084925510204</v>
+        <v>-16.67576605102041</v>
       </c>
       <c r="Q92">
-        <v>-10.70849255102043</v>
+        <v>-12.27576605102043</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8541303067248077</v>
+        <v>0.9439447852497865</v>
       </c>
       <c r="T92">
-        <v>3.971627645493014</v>
+        <v>4.41291960610335</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.3125111706351675</v>
+        <v>0.3090769819468689</v>
       </c>
       <c r="W92">
-        <v>0.1009233601507574</v>
+        <v>0.1014274990501997</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8928890589576215</v>
+        <v>0.8830770912767685</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1772540548081624</v>
+        <v>0.1782640548081625</v>
       </c>
       <c r="C93">
-        <v>2.825302540935127</v>
+        <v>-24.77981200192062</v>
       </c>
       <c r="D93">
-        <v>1466.300302540935</v>
+        <v>1455.120187998079</v>
       </c>
       <c r="E93">
-        <v>1098.175</v>
+        <v>1114.6</v>
       </c>
       <c r="F93">
-        <v>1494.675</v>
+        <v>1511.1</v>
       </c>
       <c r="G93">
         <v>31.2</v>
@@ -8907,37 +8907,37 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M93">
-        <v>219.41829</v>
+        <v>221.82948</v>
       </c>
       <c r="N93">
-        <v>-25.65502469387755</v>
+        <v>-28.06621469387758</v>
       </c>
       <c r="O93">
-        <v>-8.979258642857141</v>
+        <v>-9.823175142857153</v>
       </c>
       <c r="P93">
-        <v>-16.67576605102041</v>
+        <v>-18.24303955102043</v>
       </c>
       <c r="Q93">
-        <v>-12.27576605102043</v>
+        <v>-13.84303955102045</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9439447852497865</v>
+        <v>1.05621288340601</v>
       </c>
       <c r="T93">
-        <v>4.41291960610335</v>
+        <v>4.96453455686627</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.3090769819468689</v>
+        <v>0.3057174495344029</v>
       </c>
       <c r="W93">
-        <v>0.1014274990501997</v>
+        <v>0.1019206784083497</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8830770912767685</v>
+        <v>0.8734784272411513</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1782640548081625</v>
+        <v>0.1792740548081624</v>
       </c>
       <c r="C94">
-        <v>-24.77981200192062</v>
+        <v>-52.21572638517159</v>
       </c>
       <c r="D94">
-        <v>1455.120187998079</v>
+        <v>1444.109273614828</v>
       </c>
       <c r="E94">
-        <v>1114.6</v>
+        <v>1131.025</v>
       </c>
       <c r="F94">
-        <v>1511.1</v>
+        <v>1527.525</v>
       </c>
       <c r="G94">
         <v>31.2</v>
@@ -8989,37 +8989,37 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M94">
-        <v>221.82948</v>
+        <v>224.24067</v>
       </c>
       <c r="N94">
-        <v>-28.06621469387758</v>
+        <v>-30.47740469387756</v>
       </c>
       <c r="O94">
-        <v>-9.823175142857153</v>
+        <v>-10.66709164285714</v>
       </c>
       <c r="P94">
-        <v>-18.24303955102043</v>
+        <v>-19.81031305102042</v>
       </c>
       <c r="Q94">
-        <v>-13.84303955102045</v>
+        <v>-15.41031305102044</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.05621288340601</v>
+        <v>1.20055758103544</v>
       </c>
       <c r="T94">
-        <v>4.96453455686627</v>
+        <v>5.673753779275738</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.3057174495344029</v>
+        <v>0.3024301651308072</v>
       </c>
       <c r="W94">
-        <v>0.1019206784083497</v>
+        <v>0.1024032517587975</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8734784272411513</v>
+        <v>0.8640861860880207</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1792740548081624</v>
+        <v>0.1802840548081625</v>
       </c>
       <c r="C95">
-        <v>-52.21572638517159</v>
+        <v>-79.48625278182567</v>
       </c>
       <c r="D95">
-        <v>1444.109273614828</v>
+        <v>1433.263747218174</v>
       </c>
       <c r="E95">
-        <v>1131.025</v>
+        <v>1147.45</v>
       </c>
       <c r="F95">
-        <v>1527.525</v>
+        <v>1543.95</v>
       </c>
       <c r="G95">
         <v>31.2</v>
@@ -9071,37 +9071,37 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M95">
-        <v>224.24067</v>
+        <v>226.65186</v>
       </c>
       <c r="N95">
-        <v>-30.47740469387756</v>
+        <v>-32.88859469387756</v>
       </c>
       <c r="O95">
-        <v>-10.66709164285714</v>
+        <v>-11.51100814285715</v>
       </c>
       <c r="P95">
-        <v>-19.81031305102042</v>
+        <v>-21.37758655102042</v>
       </c>
       <c r="Q95">
-        <v>-15.41031305102044</v>
+        <v>-16.97758655102044</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.20055758103544</v>
+        <v>1.393017177874681</v>
       </c>
       <c r="T95">
-        <v>5.673753779275738</v>
+        <v>6.619379409155029</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.3024301651308072</v>
+        <v>0.2992128229485646</v>
       </c>
       <c r="W95">
-        <v>0.1024032517587975</v>
+        <v>0.1028755575911507</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8640861860880207</v>
+        <v>0.8548937798530417</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1802840548081625</v>
+        <v>0.1812940548081625</v>
       </c>
       <c r="C96">
-        <v>-79.48625278182567</v>
+        <v>-106.5950896980648</v>
       </c>
       <c r="D96">
-        <v>1433.263747218174</v>
+        <v>1422.579910301935</v>
       </c>
       <c r="E96">
-        <v>1147.45</v>
+        <v>1163.875</v>
       </c>
       <c r="F96">
-        <v>1543.95</v>
+        <v>1560.375</v>
       </c>
       <c r="G96">
         <v>31.2</v>
@@ -9153,37 +9153,37 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M96">
-        <v>226.65186</v>
+        <v>229.06305</v>
       </c>
       <c r="N96">
-        <v>-32.88859469387756</v>
+        <v>-35.29978469387757</v>
       </c>
       <c r="O96">
-        <v>-11.51100814285715</v>
+        <v>-12.35492464285715</v>
       </c>
       <c r="P96">
-        <v>-21.37758655102042</v>
+        <v>-22.94486005102042</v>
       </c>
       <c r="Q96">
-        <v>-16.97758655102044</v>
+        <v>-18.54486005102044</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.393017177874681</v>
+        <v>1.662460613449618</v>
       </c>
       <c r="T96">
-        <v>6.619379409155029</v>
+        <v>7.943255290986039</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2992128229485646</v>
+        <v>0.2960632142859481</v>
       </c>
       <c r="W96">
-        <v>0.1028755575911507</v>
+        <v>0.1033379201428228</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8548937798530417</v>
+        <v>0.8458948979598518</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1812940548081625</v>
+        <v>0.1823040548081624</v>
       </c>
       <c r="C97">
-        <v>-106.5950896980648</v>
+        <v>-133.5458261783779</v>
       </c>
       <c r="D97">
-        <v>1422.579910301935</v>
+        <v>1412.054173821622</v>
       </c>
       <c r="E97">
-        <v>1163.875</v>
+        <v>1180.3</v>
       </c>
       <c r="F97">
-        <v>1560.375</v>
+        <v>1576.8</v>
       </c>
       <c r="G97">
         <v>31.2</v>
@@ -9235,37 +9235,37 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M97">
-        <v>229.06305</v>
+        <v>231.47424</v>
       </c>
       <c r="N97">
-        <v>-35.29978469387757</v>
+        <v>-37.71097469387757</v>
       </c>
       <c r="O97">
-        <v>-12.35492464285715</v>
+        <v>-13.19884114285715</v>
       </c>
       <c r="P97">
-        <v>-22.94486005102042</v>
+        <v>-24.51213355102043</v>
       </c>
       <c r="Q97">
-        <v>-18.54486005102044</v>
+        <v>-20.11213355102045</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.662460613449618</v>
+        <v>2.066625766812022</v>
       </c>
       <c r="T97">
-        <v>7.943255290986039</v>
+        <v>9.929069113732552</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2960632142859481</v>
+        <v>0.2929792224704695</v>
       </c>
       <c r="W97">
-        <v>0.1033379201428228</v>
+        <v>0.1037906501413351</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8458948979598518</v>
+        <v>0.8370834927727701</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1823040548081625</v>
+        <v>0.1833140548081625</v>
       </c>
       <c r="C98">
-        <v>-133.5458261783781</v>
+        <v>-160.3419458253798</v>
       </c>
       <c r="D98">
-        <v>1412.054173821622</v>
+        <v>1401.68305417462</v>
       </c>
       <c r="E98">
-        <v>1180.3</v>
+        <v>1196.725</v>
       </c>
       <c r="F98">
-        <v>1576.8</v>
+        <v>1593.225</v>
       </c>
       <c r="G98">
         <v>31.2</v>
@@ -9317,37 +9317,37 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M98">
-        <v>231.47424</v>
+        <v>233.88543</v>
       </c>
       <c r="N98">
-        <v>-37.71097469387755</v>
+        <v>-40.12216469387755</v>
       </c>
       <c r="O98">
-        <v>-13.19884114285714</v>
+        <v>-14.04275764285714</v>
       </c>
       <c r="P98">
-        <v>-24.5121335510204</v>
+        <v>-26.07940705102041</v>
       </c>
       <c r="Q98">
-        <v>-20.11213355102043</v>
+        <v>-21.67940705102043</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.066625766812018</v>
+        <v>2.740234355749357</v>
       </c>
       <c r="T98">
-        <v>9.929069113732528</v>
+        <v>13.23875881831004</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2929792224704695</v>
+        <v>0.2899588181151038</v>
       </c>
       <c r="W98">
-        <v>0.1037906501413351</v>
+        <v>0.1042340455007028</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8370834927727702</v>
+        <v>0.8284537660431539</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1833140548081625</v>
+        <v>0.1843240548081624</v>
       </c>
       <c r="C99">
-        <v>-160.3419458253798</v>
+        <v>-186.9868306437738</v>
       </c>
       <c r="D99">
-        <v>1401.68305417462</v>
+        <v>1391.463169356226</v>
       </c>
       <c r="E99">
-        <v>1196.725</v>
+        <v>1213.15</v>
       </c>
       <c r="F99">
-        <v>1593.225</v>
+        <v>1609.65</v>
       </c>
       <c r="G99">
         <v>31.2</v>
@@ -9399,37 +9399,37 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M99">
-        <v>233.88543</v>
+        <v>236.29662</v>
       </c>
       <c r="N99">
-        <v>-40.12216469387755</v>
+        <v>-42.53335469387753</v>
       </c>
       <c r="O99">
-        <v>-14.04275764285714</v>
+        <v>-14.88667414285713</v>
       </c>
       <c r="P99">
-        <v>-26.07940705102041</v>
+        <v>-27.6466805510204</v>
       </c>
       <c r="Q99">
-        <v>-21.67940705102043</v>
+        <v>-23.24668055102042</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.740234355749357</v>
+        <v>4.087451533624034</v>
       </c>
       <c r="T99">
-        <v>13.23875881831004</v>
+        <v>19.85813822746505</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2899588181151038</v>
+        <v>0.2870000546649498</v>
       </c>
       <c r="W99">
-        <v>0.1042340455007028</v>
+        <v>0.1046683919751854</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8284537660431539</v>
+        <v>0.8200001561855708</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1843240548081624</v>
+        <v>0.1853340548081625</v>
       </c>
       <c r="C100">
-        <v>-186.9868306437738</v>
+        <v>-213.4837647173736</v>
       </c>
       <c r="D100">
-        <v>1391.463169356226</v>
+        <v>1381.391235282626</v>
       </c>
       <c r="E100">
-        <v>1213.15</v>
+        <v>1229.575</v>
       </c>
       <c r="F100">
-        <v>1609.65</v>
+        <v>1626.075</v>
       </c>
       <c r="G100">
         <v>31.2</v>
@@ -9481,37 +9481,37 @@
         <v>193.7632653061225</v>
       </c>
       <c r="M100">
-        <v>236.29662</v>
+        <v>238.70781</v>
       </c>
       <c r="N100">
-        <v>-42.53335469387753</v>
+        <v>-44.94454469387756</v>
       </c>
       <c r="O100">
-        <v>-14.88667414285713</v>
+        <v>-15.73059064285714</v>
       </c>
       <c r="P100">
-        <v>-27.6466805510204</v>
+        <v>-29.21395405102042</v>
       </c>
       <c r="Q100">
-        <v>-23.24668055102042</v>
+        <v>-24.81395405102044</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.087451533624034</v>
+        <v>8.129103067248069</v>
       </c>
       <c r="T100">
-        <v>19.85813822746505</v>
+        <v>39.7162764549301</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2870000546649498</v>
+        <v>0.2841010642137886</v>
       </c>
       <c r="W100">
-        <v>0.1046683919751854</v>
+        <v>0.1050939637734158</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8200001561855708</v>
+        <v>0.8117173263251104</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1853340548081625</v>
-      </c>
-      <c r="C101">
-        <v>-213.4837647173736</v>
-      </c>
-      <c r="D101">
-        <v>1381.391235282626</v>
-      </c>
-      <c r="E101">
-        <v>1229.575</v>
-      </c>
-      <c r="F101">
-        <v>1626.075</v>
-      </c>
-      <c r="G101">
-        <v>31.2</v>
-      </c>
-      <c r="H101">
-        <v>1246</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>198.1632653061224</v>
-      </c>
-      <c r="K101">
-        <v>4.399999999999977</v>
-      </c>
-      <c r="L101">
-        <v>193.7632653061225</v>
-      </c>
-      <c r="M101">
-        <v>238.70781</v>
-      </c>
-      <c r="N101">
-        <v>-44.94454469387756</v>
-      </c>
-      <c r="O101">
-        <v>-15.73059064285714</v>
-      </c>
-      <c r="P101">
-        <v>-29.21395405102042</v>
-      </c>
-      <c r="Q101">
-        <v>-24.81395405102044</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.129103067248069</v>
-      </c>
-      <c r="T101">
-        <v>39.7162764549301</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2841010642137886</v>
-      </c>
-      <c r="W101">
-        <v>0.1050939637734158</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8117173263251104</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
